--- a/Data/2011_F033_CO_RSIS/2011_F033_CO_RSIS_PlantAnalysis.xlsx
+++ b/Data/2011_F033_CO_RSIS/2011_F033_CO_RSIS_PlantAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2011_F033_CO_RSIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{090EC09D-3DD7-4E87-9629-080887BC76A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF5F69E-5F3A-4EAB-A0B6-D04669F9F8F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16215" yWindow="-24285" windowWidth="18105" windowHeight="23025" xr2:uid="{F71E01BD-9837-44DA-A92B-65CB4EFE60D7}"/>
+    <workbookView xWindow="-1320" yWindow="-27240" windowWidth="17655" windowHeight="15615" xr2:uid="{F71E01BD-9837-44DA-A92B-65CB4EFE60D7}"/>
   </bookViews>
   <sheets>
     <sheet name="PlantDF" sheetId="14" r:id="rId1"/>
@@ -28,7 +28,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">Blank!$B$1:$J$20</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'30June11'!$B:$B</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="114">
   <si>
     <t>Plant Samples</t>
   </si>
@@ -641,15 +641,18 @@
   <si>
     <t>p15-S4</t>
   </si>
+  <si>
+    <t>LAID_LAB</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="29" x14ac:knownFonts="1">
     <font>
@@ -1334,7 +1337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1350,7 +1353,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="15" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -1366,7 +1368,7 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1387,14 +1389,14 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="15" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1403,16 +1405,16 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1547,7 +1549,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1557,7 +1558,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1579,6 +1580,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="12" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -1606,14 +1615,6 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2165,7 +2166,7 @@
         <v>72</v>
       </c>
       <c r="Q1" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -2175,7 +2176,7 @@
       <c r="B2">
         <v>152</v>
       </c>
-      <c r="C2" s="100">
+      <c r="C2" s="89">
         <v>40695</v>
       </c>
       <c r="D2" t="s">
@@ -2184,40 +2185,40 @@
       <c r="E2">
         <v>18</v>
       </c>
-      <c r="F2" s="101">
+      <c r="F2" s="90">
         <v>1.375</v>
       </c>
-      <c r="G2" s="101">
+      <c r="G2" s="90">
         <v>0</v>
       </c>
-      <c r="H2" s="101">
+      <c r="H2" s="90">
         <v>0</v>
       </c>
-      <c r="I2" s="101">
+      <c r="I2" s="90">
         <v>0</v>
       </c>
-      <c r="J2" s="98">
+      <c r="J2" s="87">
         <v>1.635</v>
       </c>
-      <c r="K2" s="98">
+      <c r="K2" s="87">
         <v>1.10375</v>
       </c>
-      <c r="L2" s="98">
+      <c r="L2" s="87">
         <v>2.6594444444444445</v>
       </c>
-      <c r="M2" s="101">
+      <c r="M2" s="90">
         <v>280.25426732981703</v>
       </c>
-      <c r="N2" s="101">
+      <c r="N2" s="90">
         <v>189.19305661485356</v>
       </c>
-      <c r="O2" s="101">
+      <c r="O2" s="90">
         <v>1.7140933781640186</v>
       </c>
-      <c r="P2" s="101">
+      <c r="P2" s="90">
         <v>471.16141732283461</v>
       </c>
-      <c r="Q2" s="102">
+      <c r="Q2" s="91">
         <v>0.36313925263093816</v>
       </c>
     </row>
@@ -2228,7 +2229,7 @@
       <c r="B3">
         <v>152</v>
       </c>
-      <c r="C3" s="100">
+      <c r="C3" s="89">
         <v>40695</v>
       </c>
       <c r="D3" t="s">
@@ -2237,40 +2238,40 @@
       <c r="E3">
         <v>15</v>
       </c>
-      <c r="F3" s="101">
+      <c r="F3" s="90">
         <v>1.625</v>
       </c>
-      <c r="G3" s="101">
+      <c r="G3" s="90">
         <v>0</v>
       </c>
-      <c r="H3" s="101">
+      <c r="H3" s="90">
         <v>0</v>
       </c>
-      <c r="I3" s="101">
+      <c r="I3" s="90">
         <v>0</v>
       </c>
-      <c r="J3" s="98">
+      <c r="J3" s="87">
         <v>1.7437499999999999</v>
       </c>
-      <c r="K3" s="98">
+      <c r="K3" s="87">
         <v>1.2</v>
       </c>
-      <c r="L3" s="98">
+      <c r="L3" s="87">
         <v>2.9253333333333336</v>
       </c>
-      <c r="M3" s="101">
+      <c r="M3" s="90">
         <v>254.85880730644712</v>
       </c>
-      <c r="N3" s="101">
+      <c r="N3" s="90">
         <v>175.38670610336149</v>
       </c>
-      <c r="O3" s="101">
+      <c r="O3" s="90">
         <v>1.6442503697190136</v>
       </c>
-      <c r="P3" s="101">
+      <c r="P3" s="90">
         <v>431.88976377952758</v>
       </c>
-      <c r="Q3" s="102">
+      <c r="Q3" s="91">
         <v>0.33640631786508923</v>
       </c>
     </row>
@@ -2281,7 +2282,7 @@
       <c r="B4">
         <v>152</v>
       </c>
-      <c r="C4" s="100">
+      <c r="C4" s="89">
         <v>40695</v>
       </c>
       <c r="D4" t="s">
@@ -2290,40 +2291,40 @@
       <c r="E4">
         <v>23</v>
       </c>
-      <c r="F4" s="101">
+      <c r="F4" s="90">
         <v>0.875</v>
       </c>
-      <c r="G4" s="101">
+      <c r="G4" s="90">
         <v>0</v>
       </c>
-      <c r="H4" s="101">
+      <c r="H4" s="90">
         <v>0</v>
       </c>
-      <c r="I4" s="101">
+      <c r="I4" s="90">
         <v>0</v>
       </c>
-      <c r="J4" s="98">
+      <c r="J4" s="87">
         <v>1.3975</v>
       </c>
-      <c r="K4" s="98">
+      <c r="K4" s="87">
         <v>0.95374999999999999</v>
       </c>
-      <c r="L4" s="98">
+      <c r="L4" s="87">
         <v>2.2878260869565219</v>
       </c>
-      <c r="M4" s="101">
+      <c r="M4" s="90">
         <v>307.50247761780702</v>
       </c>
-      <c r="N4" s="101">
+      <c r="N4" s="90">
         <v>209.86081433129408</v>
       </c>
-      <c r="O4" s="101">
+      <c r="O4" s="90">
         <v>0.55009387767049567</v>
       </c>
-      <c r="P4" s="101">
+      <c r="P4" s="90">
         <v>517.91338582677167</v>
       </c>
-      <c r="Q4" s="102">
+      <c r="Q4" s="91">
         <v>0.41327177794690162</v>
       </c>
     </row>
@@ -2334,7 +2335,7 @@
       <c r="B5">
         <v>152</v>
       </c>
-      <c r="C5" s="100">
+      <c r="C5" s="89">
         <v>40695</v>
       </c>
       <c r="D5" t="s">
@@ -2343,40 +2344,40 @@
       <c r="E5">
         <v>19</v>
       </c>
-      <c r="F5" s="101">
+      <c r="F5" s="90">
         <v>1.375</v>
       </c>
-      <c r="G5" s="101">
+      <c r="G5" s="90">
         <v>0</v>
       </c>
-      <c r="H5" s="101">
+      <c r="H5" s="90">
         <v>0</v>
       </c>
-      <c r="I5" s="101">
+      <c r="I5" s="90">
         <v>0</v>
       </c>
-      <c r="J5" s="98">
+      <c r="J5" s="87">
         <v>1.4512499999999999</v>
       </c>
-      <c r="K5" s="98">
+      <c r="K5" s="87">
         <v>0.92749999999999999</v>
       </c>
-      <c r="L5" s="98">
+      <c r="L5" s="87">
         <v>2.1831578947368424</v>
       </c>
-      <c r="M5" s="101">
+      <c r="M5" s="90">
         <v>248.03705855449385</v>
       </c>
-      <c r="N5" s="101">
+      <c r="N5" s="90">
         <v>158.52153096247585</v>
       </c>
-      <c r="O5" s="101">
+      <c r="O5" s="90">
         <v>1.7091270184633516</v>
       </c>
-      <c r="P5" s="101">
+      <c r="P5" s="90">
         <v>408.26771653543307</v>
       </c>
-      <c r="Q5" s="102">
+      <c r="Q5" s="91">
         <v>0.34361144142696454</v>
       </c>
     </row>
@@ -2387,7 +2388,7 @@
       <c r="B6">
         <v>152</v>
       </c>
-      <c r="C6" s="100">
+      <c r="C6" s="89">
         <v>40695</v>
       </c>
       <c r="D6" t="s">
@@ -2396,40 +2397,40 @@
       <c r="E6">
         <v>18</v>
       </c>
-      <c r="F6" s="101">
+      <c r="F6" s="90">
         <v>1.125</v>
       </c>
-      <c r="G6" s="101">
+      <c r="G6" s="90">
         <v>0</v>
       </c>
-      <c r="H6" s="101">
+      <c r="H6" s="90">
         <v>0</v>
       </c>
-      <c r="I6" s="101">
+      <c r="I6" s="90">
         <v>0</v>
       </c>
-      <c r="J6" s="98">
+      <c r="J6" s="87">
         <v>1.6575</v>
       </c>
-      <c r="K6" s="98">
+      <c r="K6" s="87">
         <v>1.0362499999999999</v>
       </c>
-      <c r="L6" s="98">
+      <c r="L6" s="87">
         <v>2.5438888888888886</v>
       </c>
-      <c r="M6" s="101">
+      <c r="M6" s="90">
         <v>276.67295494313203</v>
       </c>
-      <c r="N6" s="101">
+      <c r="N6" s="90">
         <v>172.97275991542719</v>
       </c>
-      <c r="O6" s="101">
+      <c r="O6" s="90">
         <v>1.0432615193934089</v>
       </c>
-      <c r="P6" s="101">
+      <c r="P6" s="90">
         <v>450.68897637795271</v>
       </c>
-      <c r="Q6" s="102">
+      <c r="Q6" s="91">
         <v>0.34904817958953038</v>
       </c>
     </row>
@@ -2440,7 +2441,7 @@
       <c r="B7">
         <v>152</v>
       </c>
-      <c r="C7" s="100">
+      <c r="C7" s="89">
         <v>40695</v>
       </c>
       <c r="D7" t="s">
@@ -2449,40 +2450,40 @@
       <c r="E7">
         <v>21</v>
       </c>
-      <c r="F7" s="101">
+      <c r="F7" s="90">
         <v>1.375</v>
       </c>
-      <c r="G7" s="101">
+      <c r="G7" s="90">
         <v>0</v>
       </c>
-      <c r="H7" s="101">
+      <c r="H7" s="90">
         <v>0</v>
       </c>
-      <c r="I7" s="101">
+      <c r="I7" s="90">
         <v>0</v>
       </c>
-      <c r="J7" s="98">
+      <c r="J7" s="87">
         <v>1.35375</v>
       </c>
-      <c r="K7" s="98">
+      <c r="K7" s="87">
         <v>0.99875000000000003</v>
       </c>
-      <c r="L7" s="98">
+      <c r="L7" s="87">
         <v>2.2514285714285713</v>
       </c>
-      <c r="M7" s="101">
+      <c r="M7" s="90">
         <v>266.65541807274093</v>
       </c>
-      <c r="N7" s="101">
+      <c r="N7" s="90">
         <v>196.72915885514311</v>
       </c>
-      <c r="O7" s="101">
+      <c r="O7" s="90">
         <v>1.9697537807774028</v>
       </c>
-      <c r="P7" s="101">
+      <c r="P7" s="90">
         <v>465.35433070866139</v>
       </c>
-      <c r="Q7" s="102">
+      <c r="Q7" s="91">
         <v>0.36233867016622923</v>
       </c>
     </row>
@@ -2493,7 +2494,7 @@
       <c r="B8">
         <v>152</v>
       </c>
-      <c r="C8" s="100">
+      <c r="C8" s="89">
         <v>40695</v>
       </c>
       <c r="D8" t="s">
@@ -2502,40 +2503,40 @@
       <c r="E8">
         <v>20</v>
       </c>
-      <c r="F8" s="101">
+      <c r="F8" s="90">
         <v>1</v>
       </c>
-      <c r="G8" s="101">
+      <c r="G8" s="90">
         <v>0</v>
       </c>
-      <c r="H8" s="101">
+      <c r="H8" s="90">
         <v>0</v>
       </c>
-      <c r="I8" s="101">
+      <c r="I8" s="90">
         <v>0</v>
       </c>
-      <c r="J8" s="98">
+      <c r="J8" s="87">
         <v>1.5075000000000001</v>
       </c>
-      <c r="K8" s="98">
+      <c r="K8" s="87">
         <v>0.95250000000000001</v>
       </c>
-      <c r="L8" s="98">
+      <c r="L8" s="87">
         <v>2.5820000000000003</v>
       </c>
-      <c r="M8" s="101">
+      <c r="M8" s="90">
         <v>310.83715321588858</v>
       </c>
-      <c r="N8" s="101">
+      <c r="N8" s="90">
         <v>196.39959432048681</v>
       </c>
-      <c r="O8" s="101">
+      <c r="O8" s="90">
         <v>1.0309689990576736</v>
       </c>
-      <c r="P8" s="101">
+      <c r="P8" s="90">
         <v>508.26771653543307</v>
       </c>
-      <c r="Q8" s="102">
+      <c r="Q8" s="91">
         <v>0.4189858012170386</v>
       </c>
     </row>
@@ -2546,7 +2547,7 @@
       <c r="B9">
         <v>152</v>
       </c>
-      <c r="C9" s="100">
+      <c r="C9" s="89">
         <v>40695</v>
       </c>
       <c r="D9" t="s">
@@ -2555,40 +2556,40 @@
       <c r="E9">
         <v>17</v>
       </c>
-      <c r="F9" s="101">
+      <c r="F9" s="90">
         <v>0.625</v>
       </c>
-      <c r="G9" s="101">
+      <c r="G9" s="90">
         <v>0</v>
       </c>
-      <c r="H9" s="101">
+      <c r="H9" s="90">
         <v>0</v>
       </c>
-      <c r="I9" s="101">
+      <c r="I9" s="90">
         <v>0</v>
       </c>
-      <c r="J9" s="98">
+      <c r="J9" s="87">
         <v>1.675</v>
       </c>
-      <c r="K9" s="98">
+      <c r="K9" s="87">
         <v>1.20875</v>
       </c>
-      <c r="L9" s="98">
+      <c r="L9" s="87">
         <v>2.8823529411764701</v>
       </c>
-      <c r="M9" s="101">
+      <c r="M9" s="90">
         <v>279.64510710501298</v>
       </c>
-      <c r="N9" s="101">
+      <c r="N9" s="90">
         <v>201.80359594816983</v>
       </c>
-      <c r="O9" s="101">
+      <c r="O9" s="90">
         <v>0.83476151374630747</v>
       </c>
-      <c r="P9" s="101">
+      <c r="P9" s="90">
         <v>482.28346456692913</v>
       </c>
-      <c r="Q9" s="102">
+      <c r="Q9" s="91">
         <v>0.37652961529419376</v>
       </c>
     </row>
@@ -2599,7 +2600,7 @@
       <c r="B10">
         <v>181</v>
       </c>
-      <c r="C10" s="100">
+      <c r="C10" s="89">
         <v>40724</v>
       </c>
       <c r="D10" t="s">
@@ -2608,40 +2609,40 @@
       <c r="E10">
         <v>14</v>
       </c>
-      <c r="F10" s="101">
+      <c r="F10" s="90">
         <v>20</v>
       </c>
-      <c r="G10" s="101">
+      <c r="G10" s="90">
         <v>0.625</v>
       </c>
-      <c r="H10" s="101">
+      <c r="H10" s="90">
         <v>1.125</v>
       </c>
-      <c r="I10" s="101">
+      <c r="I10" s="90">
         <v>0</v>
       </c>
-      <c r="J10" s="98">
+      <c r="J10" s="87">
         <v>12.828749999999999</v>
       </c>
-      <c r="K10" s="98">
+      <c r="K10" s="87">
         <v>15.85125</v>
       </c>
-      <c r="L10" s="98">
+      <c r="L10" s="87">
         <v>31.57928571428571</v>
       </c>
-      <c r="M10" s="101">
+      <c r="M10" s="90">
         <v>1819.1121004859115</v>
       </c>
-      <c r="N10" s="101">
+      <c r="N10" s="90">
         <v>2247.7015050435398</v>
       </c>
-      <c r="O10" s="101">
+      <c r="O10" s="90">
         <v>284.66277242330443</v>
       </c>
-      <c r="P10" s="101">
+      <c r="P10" s="90">
         <v>4351.4763779527557</v>
       </c>
-      <c r="Q10" s="102">
+      <c r="Q10" s="91">
         <v>2.9781468880799267</v>
       </c>
     </row>
@@ -2652,7 +2653,7 @@
       <c r="B11">
         <v>181</v>
       </c>
-      <c r="C11" s="100">
+      <c r="C11" s="89">
         <v>40724</v>
       </c>
       <c r="D11" t="s">
@@ -2661,40 +2662,40 @@
       <c r="E11">
         <v>17</v>
       </c>
-      <c r="F11" s="101">
+      <c r="F11" s="90">
         <v>15.875</v>
       </c>
-      <c r="G11" s="101">
+      <c r="G11" s="90">
         <v>0.375</v>
       </c>
-      <c r="H11" s="101">
+      <c r="H11" s="90">
         <v>2.625</v>
       </c>
-      <c r="I11" s="101">
+      <c r="I11" s="90">
         <v>0</v>
       </c>
-      <c r="J11" s="98">
+      <c r="J11" s="87">
         <v>11.76375</v>
       </c>
-      <c r="K11" s="98">
+      <c r="K11" s="87">
         <v>14.155000000000001</v>
       </c>
-      <c r="L11" s="98">
+      <c r="L11" s="87">
         <v>27.856470588235297</v>
       </c>
-      <c r="M11" s="101">
+      <c r="M11" s="90">
         <v>1957.4676829437553</v>
       </c>
-      <c r="N11" s="101">
+      <c r="N11" s="90">
         <v>2355.3675530395376</v>
       </c>
-      <c r="O11" s="101">
+      <c r="O11" s="90">
         <v>348.18838606395138</v>
       </c>
-      <c r="P11" s="101">
+      <c r="P11" s="90">
         <v>4661.0236220472443</v>
       </c>
-      <c r="Q11" s="102">
+      <c r="Q11" s="91">
         <v>3.1965108225990475</v>
       </c>
     </row>
@@ -2705,7 +2706,7 @@
       <c r="B12">
         <v>181</v>
       </c>
-      <c r="C12" s="100">
+      <c r="C12" s="89">
         <v>40724</v>
       </c>
       <c r="D12" t="s">
@@ -2714,40 +2715,40 @@
       <c r="E12">
         <v>22</v>
       </c>
-      <c r="F12" s="101">
+      <c r="F12" s="90">
         <v>11.125</v>
       </c>
-      <c r="G12" s="101">
+      <c r="G12" s="90">
         <v>0.375</v>
       </c>
-      <c r="H12" s="101">
+      <c r="H12" s="90">
         <v>1.875</v>
       </c>
-      <c r="I12" s="101">
+      <c r="I12" s="90">
         <v>0</v>
       </c>
-      <c r="J12" s="98">
+      <c r="J12" s="87">
         <v>7.9050000000000002</v>
       </c>
-      <c r="K12" s="98">
+      <c r="K12" s="87">
         <v>9.4075000000000006</v>
       </c>
-      <c r="L12" s="98">
+      <c r="L12" s="87">
         <v>18.329999999999998</v>
       </c>
-      <c r="M12" s="101">
+      <c r="M12" s="90">
         <v>1664.051547554169</v>
       </c>
-      <c r="N12" s="101">
+      <c r="N12" s="90">
         <v>1980.3371200020044</v>
       </c>
-      <c r="O12" s="101">
+      <c r="O12" s="90">
         <v>324.70582063280278</v>
       </c>
-      <c r="P12" s="101">
+      <c r="P12" s="90">
         <v>3969.0944881889764</v>
       </c>
-      <c r="Q12" s="102">
+      <c r="Q12" s="91">
         <v>2.378193846741711</v>
       </c>
     </row>
@@ -2758,7 +2759,7 @@
       <c r="B13">
         <v>181</v>
       </c>
-      <c r="C13" s="100">
+      <c r="C13" s="89">
         <v>40724</v>
       </c>
       <c r="D13" t="s">
@@ -2767,40 +2768,40 @@
       <c r="E13">
         <v>19</v>
       </c>
-      <c r="F13" s="101">
+      <c r="F13" s="90">
         <v>17.375</v>
       </c>
-      <c r="G13" s="101">
+      <c r="G13" s="90">
         <v>0.375</v>
       </c>
-      <c r="H13" s="101">
+      <c r="H13" s="90">
         <v>3.375</v>
       </c>
-      <c r="I13" s="101">
+      <c r="I13" s="90">
         <v>0</v>
       </c>
-      <c r="J13" s="98">
+      <c r="J13" s="87">
         <v>10.9025</v>
       </c>
-      <c r="K13" s="98">
+      <c r="K13" s="87">
         <v>13.5725</v>
       </c>
-      <c r="L13" s="98">
+      <c r="L13" s="87">
         <v>24.450526315789478</v>
       </c>
-      <c r="M13" s="101">
+      <c r="M13" s="90">
         <v>1848.3028188005678</v>
       </c>
-      <c r="N13" s="101">
+      <c r="N13" s="90">
         <v>2300.9484070782578</v>
       </c>
-      <c r="O13" s="101">
+      <c r="O13" s="90">
         <v>423.18971900306514</v>
       </c>
-      <c r="P13" s="101">
+      <c r="P13" s="90">
         <v>4572.4409448818906</v>
       </c>
-      <c r="Q13" s="102">
+      <c r="Q13" s="91">
         <v>3.1956439472039166</v>
       </c>
     </row>
@@ -2811,7 +2812,7 @@
       <c r="B14">
         <v>181</v>
       </c>
-      <c r="C14" s="100">
+      <c r="C14" s="89">
         <v>40724</v>
       </c>
       <c r="D14" t="s">
@@ -2820,40 +2821,40 @@
       <c r="E14">
         <v>21</v>
       </c>
-      <c r="F14" s="101">
+      <c r="F14" s="90">
         <v>11.875</v>
       </c>
-      <c r="G14" s="101">
+      <c r="G14" s="90">
         <v>0.5</v>
       </c>
-      <c r="H14" s="101">
+      <c r="H14" s="90">
         <v>2.25</v>
       </c>
-      <c r="I14" s="101">
+      <c r="I14" s="90">
         <v>0</v>
       </c>
-      <c r="J14" s="98">
+      <c r="J14" s="87">
         <v>7.8987499999999997</v>
       </c>
-      <c r="K14" s="98">
+      <c r="K14" s="87">
         <v>8.9674999999999994</v>
       </c>
-      <c r="L14" s="98">
+      <c r="L14" s="87">
         <v>17.68</v>
       </c>
-      <c r="M14" s="101">
+      <c r="M14" s="90">
         <v>1543.0481622473435</v>
       </c>
-      <c r="N14" s="101">
+      <c r="N14" s="90">
         <v>1751.8321753382561</v>
       </c>
-      <c r="O14" s="101">
+      <c r="O14" s="90">
         <v>359.45037107581732</v>
       </c>
-      <c r="P14" s="101">
+      <c r="P14" s="90">
         <v>3654.3307086614172</v>
       </c>
-      <c r="Q14" s="102">
+      <c r="Q14" s="91">
         <v>2.2822168261376281</v>
       </c>
     </row>
@@ -2864,7 +2865,7 @@
       <c r="B15">
         <v>181</v>
       </c>
-      <c r="C15" s="100">
+      <c r="C15" s="89">
         <v>40724</v>
       </c>
       <c r="D15" t="s">
@@ -2873,40 +2874,40 @@
       <c r="E15">
         <v>17</v>
       </c>
-      <c r="F15" s="101">
+      <c r="F15" s="90">
         <v>16.25</v>
       </c>
-      <c r="G15" s="101">
+      <c r="G15" s="90">
         <v>0.875</v>
       </c>
-      <c r="H15" s="101">
+      <c r="H15" s="90">
         <v>3.125</v>
       </c>
-      <c r="I15" s="101">
+      <c r="I15" s="90">
         <v>0</v>
       </c>
-      <c r="J15" s="98">
+      <c r="J15" s="87">
         <v>10.255000000000001</v>
       </c>
-      <c r="K15" s="98">
+      <c r="K15" s="87">
         <v>12.170000000000002</v>
       </c>
-      <c r="L15" s="98">
+      <c r="L15" s="87">
         <v>22.231764705882352</v>
       </c>
-      <c r="M15" s="101">
+      <c r="M15" s="90">
         <v>1480.8050377806805</v>
       </c>
-      <c r="N15" s="101">
+      <c r="N15" s="90">
         <v>1757.3278702867754</v>
       </c>
-      <c r="O15" s="101">
+      <c r="O15" s="90">
         <v>481.74898169632331</v>
       </c>
-      <c r="P15" s="101">
+      <c r="P15" s="90">
         <v>3719.8818897637793</v>
       </c>
-      <c r="Q15" s="102">
+      <c r="Q15" s="91">
         <v>2.1029814109193943</v>
       </c>
     </row>
@@ -2917,7 +2918,7 @@
       <c r="B16">
         <v>181</v>
       </c>
-      <c r="C16" s="100">
+      <c r="C16" s="89">
         <v>40724</v>
       </c>
       <c r="D16" t="s">
@@ -2926,40 +2927,40 @@
       <c r="E16">
         <v>17</v>
       </c>
-      <c r="F16" s="101">
+      <c r="F16" s="90">
         <v>12.75</v>
       </c>
-      <c r="G16" s="101">
+      <c r="G16" s="90">
         <v>0.375</v>
       </c>
-      <c r="H16" s="101">
+      <c r="H16" s="90">
         <v>3.5</v>
       </c>
-      <c r="I16" s="101">
+      <c r="I16" s="90">
         <v>0</v>
       </c>
-      <c r="J16" s="98">
+      <c r="J16" s="87">
         <v>11.20875</v>
       </c>
-      <c r="K16" s="98">
+      <c r="K16" s="87">
         <v>13.442500000000001</v>
       </c>
-      <c r="L16" s="98">
+      <c r="L16" s="87">
         <v>25.898823529411768</v>
       </c>
-      <c r="M16" s="101">
+      <c r="M16" s="90">
         <v>1780.1171272918389</v>
       </c>
-      <c r="N16" s="101">
+      <c r="N16" s="90">
         <v>2134.8700331098958</v>
       </c>
-      <c r="O16" s="101">
+      <c r="O16" s="90">
         <v>418.47740652740003</v>
       </c>
-      <c r="P16" s="101">
+      <c r="P16" s="90">
         <v>4333.464566929134</v>
       </c>
-      <c r="Q16" s="102">
+      <c r="Q16" s="91">
         <v>2.9603107619243785</v>
       </c>
     </row>
@@ -2970,7 +2971,7 @@
       <c r="B17">
         <v>181</v>
       </c>
-      <c r="C17" s="100">
+      <c r="C17" s="89">
         <v>40724</v>
       </c>
       <c r="D17" t="s">
@@ -2979,40 +2980,40 @@
       <c r="E17">
         <v>17</v>
       </c>
-      <c r="F17" s="101">
+      <c r="F17" s="90">
         <v>13.125</v>
       </c>
-      <c r="G17" s="101">
+      <c r="G17" s="90">
         <v>0.625</v>
       </c>
-      <c r="H17" s="101">
+      <c r="H17" s="90">
         <v>2.375</v>
       </c>
-      <c r="I17" s="101">
+      <c r="I17" s="90">
         <v>0</v>
       </c>
-      <c r="J17" s="98">
+      <c r="J17" s="87">
         <v>10.4825</v>
       </c>
-      <c r="K17" s="98">
+      <c r="K17" s="87">
         <v>12.305</v>
       </c>
-      <c r="L17" s="98">
+      <c r="L17" s="87">
         <v>24.799411764705884</v>
       </c>
-      <c r="M17" s="101">
+      <c r="M17" s="90">
         <v>1742.3279106497127</v>
       </c>
-      <c r="N17" s="101">
+      <c r="N17" s="90">
         <v>2045.2511271685873</v>
       </c>
-      <c r="O17" s="101">
+      <c r="O17" s="90">
         <v>361.92883619744816</v>
       </c>
-      <c r="P17" s="101">
+      <c r="P17" s="90">
         <v>4149.5078740157478</v>
       </c>
-      <c r="Q17" s="102">
+      <c r="Q17" s="91">
         <v>2.7915475563426599</v>
       </c>
     </row>
@@ -3023,7 +3024,7 @@
       <c r="B18">
         <v>208</v>
       </c>
-      <c r="C18" s="100">
+      <c r="C18" s="89">
         <v>40751</v>
       </c>
       <c r="D18" t="s">
@@ -3032,40 +3033,40 @@
       <c r="E18">
         <v>16</v>
       </c>
-      <c r="F18" s="101">
+      <c r="F18" s="90">
         <v>3.25</v>
       </c>
-      <c r="G18" s="101">
+      <c r="G18" s="90">
         <v>0.375</v>
       </c>
-      <c r="H18" s="101">
+      <c r="H18" s="90">
         <v>6.5</v>
       </c>
-      <c r="I18" s="101">
+      <c r="I18" s="90">
         <v>0</v>
       </c>
-      <c r="J18" s="98">
+      <c r="J18" s="87">
         <v>12.834999999999999</v>
       </c>
-      <c r="K18" s="98">
+      <c r="K18" s="87">
         <v>15.87</v>
       </c>
-      <c r="L18" s="98">
+      <c r="L18" s="87">
         <v>50.936875000000001</v>
       </c>
-      <c r="M18" s="101">
+      <c r="M18" s="90">
         <v>2308.0571639510144</v>
       </c>
-      <c r="N18" s="101">
+      <c r="N18" s="90">
         <v>2853.8268166655707</v>
       </c>
-      <c r="O18" s="101">
+      <c r="O18" s="90">
         <v>2859.6711374936513</v>
       </c>
-      <c r="P18" s="101">
+      <c r="P18" s="90">
         <v>8021.5551181102364</v>
       </c>
-      <c r="Q18" s="102">
+      <c r="Q18" s="91">
         <v>3.7974598488301949</v>
       </c>
     </row>
@@ -3076,7 +3077,7 @@
       <c r="B19">
         <v>208</v>
       </c>
-      <c r="C19" s="100">
+      <c r="C19" s="89">
         <v>40751</v>
       </c>
       <c r="D19" t="s">
@@ -3085,40 +3086,40 @@
       <c r="E19">
         <v>19</v>
       </c>
-      <c r="F19" s="101">
+      <c r="F19" s="90">
         <v>1.625</v>
       </c>
-      <c r="G19" s="101">
+      <c r="G19" s="90">
         <v>0.125</v>
       </c>
-      <c r="H19" s="101">
+      <c r="H19" s="90">
         <v>6.75</v>
       </c>
-      <c r="I19" s="101">
+      <c r="I19" s="90">
         <v>0</v>
       </c>
-      <c r="J19" s="98">
+      <c r="J19" s="87">
         <v>12.848749999999999</v>
       </c>
-      <c r="K19" s="98">
+      <c r="K19" s="87">
         <v>13.807499999999999</v>
       </c>
-      <c r="L19" s="98">
+      <c r="L19" s="87">
         <v>43.094210526315784</v>
       </c>
-      <c r="M19" s="101">
+      <c r="M19" s="90">
         <v>2418.6281998965455</v>
       </c>
-      <c r="N19" s="101">
+      <c r="N19" s="90">
         <v>2599.1017702166791</v>
       </c>
-      <c r="O19" s="101">
+      <c r="O19" s="90">
         <v>3041.2267228001615</v>
       </c>
-      <c r="P19" s="101">
+      <c r="P19" s="90">
         <v>8058.9566929133862</v>
       </c>
-      <c r="Q19" s="102">
+      <c r="Q19" s="91">
         <v>4.0271253664003677</v>
       </c>
     </row>
@@ -3129,7 +3130,7 @@
       <c r="B20">
         <v>208</v>
       </c>
-      <c r="C20" s="100">
+      <c r="C20" s="89">
         <v>40751</v>
       </c>
       <c r="D20" t="s">
@@ -3138,40 +3139,40 @@
       <c r="E20">
         <v>18</v>
       </c>
-      <c r="F20" s="101">
+      <c r="F20" s="90">
         <v>2.5</v>
       </c>
-      <c r="G20" s="101">
+      <c r="G20" s="90">
         <v>0.125</v>
       </c>
-      <c r="H20" s="101">
+      <c r="H20" s="90">
         <v>8.875</v>
       </c>
-      <c r="I20" s="101">
+      <c r="I20" s="90">
         <v>0</v>
       </c>
-      <c r="J20" s="98">
+      <c r="J20" s="87">
         <v>12.77</v>
       </c>
-      <c r="K20" s="98">
+      <c r="K20" s="87">
         <v>16.628749999999997</v>
       </c>
-      <c r="L20" s="98">
+      <c r="L20" s="87">
         <v>46.062777777777775</v>
       </c>
-      <c r="M20" s="101">
+      <c r="M20" s="90">
         <v>2245.1727785905141</v>
       </c>
-      <c r="N20" s="101">
+      <c r="N20" s="90">
         <v>2923.6035115103373</v>
       </c>
-      <c r="O20" s="101">
+      <c r="O20" s="90">
         <v>2991.9520563558399</v>
       </c>
-      <c r="P20" s="101">
+      <c r="P20" s="90">
         <v>8160.7283464566926</v>
       </c>
-      <c r="Q20" s="102">
+      <c r="Q20" s="91">
         <v>4.0881660167718046</v>
       </c>
     </row>
@@ -3182,7 +3183,7 @@
       <c r="B21">
         <v>208</v>
       </c>
-      <c r="C21" s="100">
+      <c r="C21" s="89">
         <v>40751</v>
       </c>
       <c r="D21" t="s">
@@ -3191,40 +3192,40 @@
       <c r="E21">
         <v>19</v>
       </c>
-      <c r="F21" s="101">
+      <c r="F21" s="90">
         <v>3.875</v>
       </c>
-      <c r="G21" s="101">
+      <c r="G21" s="90">
         <v>0.25</v>
       </c>
-      <c r="H21" s="101">
+      <c r="H21" s="90">
         <v>8.375</v>
       </c>
-      <c r="I21" s="101">
+      <c r="I21" s="90">
         <v>0</v>
       </c>
-      <c r="J21" s="98">
+      <c r="J21" s="87">
         <v>14.84</v>
       </c>
-      <c r="K21" s="98">
+      <c r="K21" s="87">
         <v>18.483750000000001</v>
       </c>
-      <c r="L21" s="98">
+      <c r="L21" s="87">
         <v>57.744210526315797</v>
       </c>
-      <c r="M21" s="101">
+      <c r="M21" s="90">
         <v>2968.0335450498196</v>
       </c>
-      <c r="N21" s="101">
+      <c r="N21" s="90">
         <v>3696.7917815575879</v>
       </c>
-      <c r="O21" s="101">
+      <c r="O21" s="90">
         <v>4133.7967206366884</v>
       </c>
-      <c r="P21" s="101">
+      <c r="P21" s="90">
         <v>10798.622047244095</v>
       </c>
-      <c r="Q21" s="102">
+      <c r="Q21" s="91">
         <v>5.4968121255904983</v>
       </c>
     </row>
@@ -3235,7 +3236,7 @@
       <c r="B22">
         <v>208</v>
       </c>
-      <c r="C22" s="100">
+      <c r="C22" s="89">
         <v>40751</v>
       </c>
       <c r="D22" t="s">
@@ -3244,40 +3245,40 @@
       <c r="E22">
         <v>15</v>
       </c>
-      <c r="F22" s="101">
+      <c r="F22" s="90">
         <v>11</v>
       </c>
-      <c r="G22" s="101">
+      <c r="G22" s="90">
         <v>0.25</v>
       </c>
-      <c r="H22" s="101">
+      <c r="H22" s="90">
         <v>9.125</v>
       </c>
-      <c r="I22" s="101">
+      <c r="I22" s="90">
         <v>0</v>
       </c>
-      <c r="J22" s="98">
+      <c r="J22" s="87">
         <v>18.901249999999997</v>
       </c>
-      <c r="K22" s="98">
+      <c r="K22" s="87">
         <v>24.778750000000002</v>
       </c>
-      <c r="L22" s="98">
+      <c r="L22" s="87">
         <v>67.028666666666652</v>
       </c>
-      <c r="M22" s="101">
+      <c r="M22" s="90">
         <v>2882.9546897452096</v>
       </c>
-      <c r="N22" s="101">
+      <c r="N22" s="90">
         <v>3779.4332924290266</v>
       </c>
-      <c r="O22" s="101">
+      <c r="O22" s="90">
         <v>3233.5765847548946</v>
       </c>
-      <c r="P22" s="101">
+      <c r="P22" s="90">
         <v>9895.9645669291313</v>
       </c>
-      <c r="Q22" s="102">
+      <c r="Q22" s="91">
         <v>5.6499887094709056</v>
       </c>
     </row>
@@ -3288,7 +3289,7 @@
       <c r="B23">
         <v>208</v>
       </c>
-      <c r="C23" s="100">
+      <c r="C23" s="89">
         <v>40751</v>
       </c>
       <c r="D23" t="s">
@@ -3297,40 +3298,40 @@
       <c r="E23">
         <v>14</v>
       </c>
-      <c r="F23" s="101">
+      <c r="F23" s="90">
         <v>5.875</v>
       </c>
-      <c r="G23" s="101">
+      <c r="G23" s="90">
         <v>0.375</v>
       </c>
-      <c r="H23" s="101">
+      <c r="H23" s="90">
         <v>8</v>
       </c>
-      <c r="I23" s="101">
+      <c r="I23" s="90">
         <v>0</v>
       </c>
-      <c r="J23" s="98">
+      <c r="J23" s="87">
         <v>18.270000000000003</v>
       </c>
-      <c r="K23" s="98">
+      <c r="K23" s="87">
         <v>22.353750000000002</v>
       </c>
-      <c r="L23" s="98">
+      <c r="L23" s="87">
         <v>58.932857142857138</v>
       </c>
-      <c r="M23" s="101">
+      <c r="M23" s="90">
         <v>2571.0322183949897</v>
       </c>
-      <c r="N23" s="101">
+      <c r="N23" s="90">
         <v>3145.7149125313081</v>
       </c>
-      <c r="O23" s="101">
+      <c r="O23" s="90">
         <v>2403.9221604122827</v>
       </c>
-      <c r="P23" s="101">
+      <c r="P23" s="90">
         <v>8120.6692913385814</v>
       </c>
-      <c r="Q23" s="102">
+      <c r="Q23" s="91">
         <v>4.7323809367460594</v>
       </c>
     </row>
@@ -3341,7 +3342,7 @@
       <c r="B24">
         <v>208</v>
       </c>
-      <c r="C24" s="100">
+      <c r="C24" s="89">
         <v>40751</v>
       </c>
       <c r="D24" t="s">
@@ -3350,40 +3351,40 @@
       <c r="E24">
         <v>18</v>
       </c>
-      <c r="F24" s="101">
+      <c r="F24" s="90">
         <v>1.375</v>
       </c>
-      <c r="G24" s="101">
+      <c r="G24" s="90">
         <v>0.25</v>
       </c>
-      <c r="H24" s="101">
+      <c r="H24" s="90">
         <v>8.375</v>
       </c>
-      <c r="I24" s="101">
+      <c r="I24" s="90">
         <v>0</v>
       </c>
-      <c r="J24" s="98">
+      <c r="J24" s="87">
         <v>13.59125</v>
       </c>
-      <c r="K24" s="98">
+      <c r="K24" s="87">
         <v>14.719999999999999</v>
       </c>
-      <c r="L24" s="98">
+      <c r="L24" s="87">
         <v>47.164444444444449</v>
       </c>
-      <c r="M24" s="101">
+      <c r="M24" s="90">
         <v>2419.6697728220215</v>
       </c>
-      <c r="N24" s="101">
+      <c r="N24" s="90">
         <v>2620.6227577257541</v>
       </c>
-      <c r="O24" s="101">
+      <c r="O24" s="90">
         <v>3315.6129812632485</v>
       </c>
-      <c r="P24" s="101">
+      <c r="P24" s="90">
         <v>8355.9055118110246</v>
       </c>
-      <c r="Q24" s="102">
+      <c r="Q24" s="91">
         <v>4.2569542062275776</v>
       </c>
     </row>
@@ -3394,7 +3395,7 @@
       <c r="B25">
         <v>208</v>
       </c>
-      <c r="C25" s="100">
+      <c r="C25" s="89">
         <v>40751</v>
       </c>
       <c r="D25" t="s">
@@ -3403,40 +3404,40 @@
       <c r="E25">
         <v>16</v>
       </c>
-      <c r="F25" s="101">
+      <c r="F25" s="90">
         <v>2.5</v>
       </c>
-      <c r="G25" s="101">
+      <c r="G25" s="90">
         <v>0.375</v>
       </c>
-      <c r="H25" s="101">
+      <c r="H25" s="90">
         <v>7.25</v>
       </c>
-      <c r="I25" s="101">
+      <c r="I25" s="90">
         <v>0</v>
       </c>
-      <c r="J25" s="98">
+      <c r="J25" s="87">
         <v>13.09125</v>
       </c>
-      <c r="K25" s="98">
+      <c r="K25" s="87">
         <v>17.422500000000003</v>
       </c>
-      <c r="L25" s="98">
+      <c r="L25" s="87">
         <v>46.409374999999997</v>
       </c>
-      <c r="M25" s="101">
+      <c r="M25" s="90">
         <v>2057.7068717816933</v>
       </c>
-      <c r="N25" s="101">
+      <c r="N25" s="90">
         <v>2738.5007523052841</v>
       </c>
-      <c r="O25" s="101">
+      <c r="O25" s="90">
         <v>2512.355368039006</v>
       </c>
-      <c r="P25" s="101">
+      <c r="P25" s="90">
         <v>7308.5629921259833</v>
       </c>
-      <c r="Q25" s="102">
+      <c r="Q25" s="91">
         <v>3.1200596890951293</v>
       </c>
     </row>
@@ -3447,7 +3448,7 @@
       <c r="B26">
         <v>236</v>
       </c>
-      <c r="C26" s="100">
+      <c r="C26" s="89">
         <v>40779</v>
       </c>
       <c r="D26" t="s">
@@ -3456,40 +3457,40 @@
       <c r="E26">
         <v>14</v>
       </c>
-      <c r="F26" s="101">
+      <c r="F26" s="90">
         <v>4.5</v>
       </c>
-      <c r="G26" s="101">
+      <c r="G26" s="90">
         <v>0.125</v>
       </c>
-      <c r="H26" s="101">
+      <c r="H26" s="90">
         <v>11.125</v>
       </c>
-      <c r="I26" s="101">
+      <c r="I26" s="90">
         <v>3.25</v>
       </c>
-      <c r="J26" s="98">
+      <c r="J26" s="87">
         <v>22.8825</v>
       </c>
-      <c r="K26" s="98">
+      <c r="K26" s="87">
         <v>32.251249999999999</v>
       </c>
-      <c r="L26" s="98">
+      <c r="L26" s="87">
         <v>103.15999999999998</v>
       </c>
-      <c r="M26" s="101">
+      <c r="M26" s="90">
         <v>3247.015501320654</v>
       </c>
-      <c r="N26" s="101">
+      <c r="N26" s="90">
         <v>4576.4365207895871</v>
       </c>
-      <c r="O26" s="101">
+      <c r="O26" s="90">
         <v>6391.5086078110144</v>
       </c>
-      <c r="P26" s="101">
+      <c r="P26" s="90">
         <v>14214.960629921256</v>
       </c>
-      <c r="Q26" s="102">
+      <c r="Q26" s="91">
         <v>5.8079468794517375</v>
       </c>
     </row>
@@ -3500,7 +3501,7 @@
       <c r="B27">
         <v>236</v>
       </c>
-      <c r="C27" s="100">
+      <c r="C27" s="89">
         <v>40779</v>
       </c>
       <c r="D27" t="s">
@@ -3509,40 +3510,40 @@
       <c r="E27">
         <v>13</v>
       </c>
-      <c r="F27" s="101">
+      <c r="F27" s="90">
         <v>13</v>
       </c>
-      <c r="G27" s="101">
+      <c r="G27" s="90">
         <v>0.375</v>
       </c>
-      <c r="H27" s="101">
+      <c r="H27" s="90">
         <v>11.875</v>
       </c>
-      <c r="I27" s="101">
+      <c r="I27" s="90">
         <v>4.25</v>
       </c>
-      <c r="J27" s="98">
+      <c r="J27" s="87">
         <v>25.033750000000001</v>
       </c>
-      <c r="K27" s="98">
+      <c r="K27" s="87">
         <v>32.626249999999999</v>
       </c>
-      <c r="L27" s="98">
+      <c r="L27" s="87">
         <v>110.42</v>
       </c>
-      <c r="M27" s="101">
+      <c r="M27" s="90">
         <v>3178.7040028200149</v>
       </c>
-      <c r="N27" s="101">
+      <c r="N27" s="90">
         <v>4142.7749127480511</v>
       </c>
-      <c r="O27" s="101">
+      <c r="O27" s="90">
         <v>6807.0643915185492</v>
       </c>
-      <c r="P27" s="101">
+      <c r="P27" s="90">
         <v>14128.543307086615</v>
       </c>
-      <c r="Q27" s="102">
+      <c r="Q27" s="91">
         <v>5.5974522076921476</v>
       </c>
     </row>
@@ -3553,7 +3554,7 @@
       <c r="B28">
         <v>236</v>
       </c>
-      <c r="C28" s="100">
+      <c r="C28" s="89">
         <v>40779</v>
       </c>
       <c r="D28" t="s">
@@ -3562,40 +3563,40 @@
       <c r="E28">
         <v>15</v>
       </c>
-      <c r="F28" s="101">
+      <c r="F28" s="90">
         <v>14</v>
       </c>
-      <c r="G28" s="101">
+      <c r="G28" s="90">
         <v>0.875</v>
       </c>
-      <c r="H28" s="101">
+      <c r="H28" s="90">
         <v>7.5</v>
       </c>
-      <c r="I28" s="101">
+      <c r="I28" s="90">
         <v>4.125</v>
       </c>
-      <c r="J28" s="98">
+      <c r="J28" s="87">
         <v>21.85125</v>
       </c>
-      <c r="K28" s="98">
+      <c r="K28" s="87">
         <v>26.39</v>
       </c>
-      <c r="L28" s="98">
+      <c r="L28" s="87">
         <v>96.420666666666662</v>
       </c>
-      <c r="M28" s="101">
+      <c r="M28" s="90">
         <v>3484.4348676217824</v>
       </c>
-      <c r="N28" s="101">
+      <c r="N28" s="90">
         <v>4208.1911175122177</v>
       </c>
-      <c r="O28" s="101">
+      <c r="O28" s="90">
         <v>6542.7086605352897</v>
       </c>
-      <c r="P28" s="101">
+      <c r="P28" s="90">
         <v>14235.334645669291</v>
       </c>
-      <c r="Q28" s="102">
+      <c r="Q28" s="91">
         <v>6.1924911636866256</v>
       </c>
     </row>
@@ -3606,7 +3607,7 @@
       <c r="B29">
         <v>236</v>
       </c>
-      <c r="C29" s="100">
+      <c r="C29" s="89">
         <v>40779</v>
       </c>
       <c r="D29" t="s">
@@ -3615,40 +3616,40 @@
       <c r="E29">
         <v>20</v>
       </c>
-      <c r="F29" s="101">
+      <c r="F29" s="90">
         <v>6.125</v>
       </c>
-      <c r="G29" s="101">
+      <c r="G29" s="90">
         <v>0</v>
       </c>
-      <c r="H29" s="101">
+      <c r="H29" s="90">
         <v>4.625</v>
       </c>
-      <c r="I29" s="101">
+      <c r="I29" s="90">
         <v>0.4</v>
       </c>
-      <c r="J29" s="98">
+      <c r="J29" s="87">
         <v>14.78875</v>
       </c>
-      <c r="K29" s="98">
+      <c r="K29" s="87">
         <v>19.172499999999999</v>
       </c>
-      <c r="L29" s="98">
+      <c r="L29" s="87">
         <v>75.358000000000004</v>
       </c>
-      <c r="M29" s="101">
+      <c r="M29" s="90">
         <v>3265.4951165572625</v>
       </c>
-      <c r="N29" s="101">
+      <c r="N29" s="90">
         <v>4233.4683541336562</v>
       </c>
-      <c r="O29" s="101">
+      <c r="O29" s="90">
         <v>7335.2884978130169</v>
       </c>
-      <c r="P29" s="101">
+      <c r="P29" s="90">
         <v>14834.251968503937</v>
       </c>
-      <c r="Q29" s="102">
+      <c r="Q29" s="91">
         <v>5.5425921253982242</v>
       </c>
     </row>
@@ -3659,7 +3660,7 @@
       <c r="B30">
         <v>236</v>
       </c>
-      <c r="C30" s="100">
+      <c r="C30" s="89">
         <v>40779</v>
       </c>
       <c r="D30" t="s">
@@ -3668,40 +3669,40 @@
       <c r="E30">
         <v>17</v>
       </c>
-      <c r="F30" s="101">
+      <c r="F30" s="90">
         <v>15.875</v>
       </c>
-      <c r="G30" s="101">
+      <c r="G30" s="90">
         <v>0.375</v>
       </c>
-      <c r="H30" s="101">
+      <c r="H30" s="90">
         <v>6.75</v>
       </c>
-      <c r="I30" s="101">
+      <c r="I30" s="90">
         <v>3.625</v>
       </c>
-      <c r="J30" s="98">
+      <c r="J30" s="87">
         <v>21.116250000000001</v>
       </c>
-      <c r="K30" s="98">
+      <c r="K30" s="87">
         <v>26.033749999999998</v>
       </c>
-      <c r="L30" s="98">
+      <c r="L30" s="87">
         <v>79.590000000000018</v>
       </c>
-      <c r="M30" s="101">
+      <c r="M30" s="90">
         <v>3550.3491193690352</v>
       </c>
-      <c r="N30" s="101">
+      <c r="N30" s="90">
         <v>4377.1456289053986</v>
       </c>
-      <c r="O30" s="101">
+      <c r="O30" s="90">
         <v>5389.7296611743859</v>
       </c>
-      <c r="P30" s="101">
+      <c r="P30" s="90">
         <v>13317.22440944882</v>
       </c>
-      <c r="Q30" s="102">
+      <c r="Q30" s="91">
         <v>8.061160884539083</v>
       </c>
     </row>
@@ -3712,7 +3713,7 @@
       <c r="B31">
         <v>236</v>
       </c>
-      <c r="C31" s="100">
+      <c r="C31" s="89">
         <v>40779</v>
       </c>
       <c r="D31" t="s">
@@ -3721,40 +3722,40 @@
       <c r="E31">
         <v>17</v>
       </c>
-      <c r="F31" s="101">
+      <c r="F31" s="90">
         <v>8.25</v>
       </c>
-      <c r="G31" s="101">
+      <c r="G31" s="90">
         <v>0.75</v>
       </c>
-      <c r="H31" s="101">
+      <c r="H31" s="90">
         <v>7.5</v>
       </c>
-      <c r="I31" s="101">
+      <c r="I31" s="90">
         <v>1.875</v>
       </c>
-      <c r="J31" s="98">
+      <c r="J31" s="87">
         <v>18.59375</v>
       </c>
-      <c r="K31" s="98">
+      <c r="K31" s="87">
         <v>24.1675</v>
       </c>
-      <c r="L31" s="98">
+      <c r="L31" s="87">
         <v>86.729411764705887</v>
       </c>
-      <c r="M31" s="101">
+      <c r="M31" s="90">
         <v>3264.4222994945703</v>
       </c>
-      <c r="N31" s="101">
+      <c r="N31" s="90">
         <v>4242.9808899783548</v>
       </c>
-      <c r="O31" s="101">
+      <c r="O31" s="90">
         <v>7004.4078341491231</v>
       </c>
-      <c r="P31" s="101">
+      <c r="P31" s="90">
         <v>14511.811023622047</v>
       </c>
-      <c r="Q31" s="102">
+      <c r="Q31" s="91">
         <v>5.8274601506405928</v>
       </c>
     </row>
@@ -3765,7 +3766,7 @@
       <c r="B32">
         <v>236</v>
       </c>
-      <c r="C32" s="100">
+      <c r="C32" s="89">
         <v>40779</v>
       </c>
       <c r="D32" t="s">
@@ -3774,40 +3775,40 @@
       <c r="E32">
         <v>17</v>
       </c>
-      <c r="F32" s="101">
+      <c r="F32" s="90">
         <v>12.125</v>
       </c>
-      <c r="G32" s="101">
+      <c r="G32" s="90">
         <v>0.25</v>
       </c>
-      <c r="H32" s="101">
+      <c r="H32" s="90">
         <v>7.875</v>
       </c>
-      <c r="I32" s="101">
+      <c r="I32" s="90">
         <v>1.875</v>
       </c>
-      <c r="J32" s="98">
+      <c r="J32" s="87">
         <v>15.606249999999999</v>
       </c>
-      <c r="K32" s="98">
+      <c r="K32" s="87">
         <v>23.598749999999999</v>
       </c>
-      <c r="L32" s="98">
+      <c r="L32" s="87">
         <v>68.322352941176476</v>
       </c>
-      <c r="M32" s="101">
+      <c r="M32" s="90">
         <v>2873.218796190989</v>
       </c>
-      <c r="N32" s="101">
+      <c r="N32" s="90">
         <v>4344.693444396451</v>
       </c>
-      <c r="O32" s="101">
+      <c r="O32" s="90">
         <v>4213.9775231920876</v>
       </c>
-      <c r="P32" s="101">
+      <c r="P32" s="90">
         <v>11431.889763779527</v>
       </c>
-      <c r="Q32" s="102">
+      <c r="Q32" s="91">
         <v>5.4403598191393661</v>
       </c>
     </row>
@@ -3818,7 +3819,7 @@
       <c r="B33">
         <v>236</v>
       </c>
-      <c r="C33" s="100">
+      <c r="C33" s="89">
         <v>40779</v>
       </c>
       <c r="D33" t="s">
@@ -3827,40 +3828,40 @@
       <c r="E33">
         <v>20</v>
       </c>
-      <c r="F33" s="101">
+      <c r="F33" s="90">
         <v>14.25</v>
       </c>
-      <c r="G33" s="101">
+      <c r="G33" s="90">
         <v>0.25</v>
       </c>
-      <c r="H33" s="101">
+      <c r="H33" s="90">
         <v>10.75</v>
       </c>
-      <c r="I33" s="101">
+      <c r="I33" s="90">
         <v>1.75</v>
       </c>
-      <c r="J33" s="98">
+      <c r="J33" s="87">
         <v>22.47</v>
       </c>
-      <c r="K33" s="98">
+      <c r="K33" s="87">
         <v>31.015000000000001</v>
       </c>
-      <c r="L33" s="98">
+      <c r="L33" s="87">
         <v>68.216000000000008</v>
       </c>
-      <c r="M33" s="101">
+      <c r="M33" s="90">
         <v>3493.7178820342697</v>
       </c>
-      <c r="N33" s="101">
+      <c r="N33" s="90">
         <v>4822.3257726432084</v>
       </c>
-      <c r="O33" s="101">
+      <c r="O33" s="90">
         <v>5112.3028020154343</v>
       </c>
-      <c r="P33" s="101">
+      <c r="P33" s="90">
         <v>13428.346456692914</v>
       </c>
-      <c r="Q33" s="102">
+      <c r="Q33" s="91">
         <v>5.6708778572538909</v>
       </c>
     </row>
@@ -3911,11 +3912,9 @@
         <v>1</v>
       </c>
       <c r="D5" s="6"/>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>40695</v>
       </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
     </row>
     <row r="6" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C6" s="5" t="s">
@@ -3925,25 +3924,21 @@
       <c r="E6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
     </row>
     <row r="8" spans="2:32" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="5" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="6"/>
-      <c r="E8" s="9">
+      <c r="E8" s="8">
         <v>40695</v>
       </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
       <c r="J8" s="5" t="s">
         <v>5</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
-      <c r="M8" s="9">
+      <c r="M8" s="8">
         <v>40701</v>
       </c>
     </row>
@@ -3955,152 +3950,146 @@
       <c r="E9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
     </row>
     <row r="10" spans="2:32" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="5"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
     </row>
     <row r="11" spans="2:32" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D11" s="8"/>
-      <c r="E11" s="10" t="s">
+      <c r="D11" s="7"/>
+      <c r="E11" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="18"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
     </row>
     <row r="12" spans="2:32" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="13" t="s">
+      <c r="D12" s="13"/>
+      <c r="E12" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="38" t="s">
+      <c r="G12" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="H12" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="I12" s="14"/>
-      <c r="J12" s="23" t="s">
+      <c r="I12" s="13"/>
+      <c r="J12" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="K12" s="13" t="s">
+      <c r="K12" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="L12" s="13" t="s">
+      <c r="L12" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="15" t="s">
+      <c r="M12" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="N12" s="15" t="s">
+      <c r="N12" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="O12" s="15" t="s">
+      <c r="O12" s="14" t="s">
         <v>12</v>
       </c>
       <c r="S12" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="T12" s="97" t="s">
+      <c r="T12" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="U12" s="97" t="s">
+      <c r="U12" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="V12" s="97" t="s">
+      <c r="V12" s="86" t="s">
         <v>74</v>
       </c>
-      <c r="W12" s="97" t="s">
+      <c r="W12" s="86" t="s">
         <v>75</v>
       </c>
-      <c r="X12" s="97" t="s">
+      <c r="X12" s="86" t="s">
         <v>66</v>
       </c>
-      <c r="Y12" s="97" t="s">
+      <c r="Y12" s="86" t="s">
         <v>67</v>
       </c>
-      <c r="Z12" s="97" t="s">
+      <c r="Z12" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="AA12" s="97" t="s">
+      <c r="AA12" s="86" t="s">
         <v>69</v>
       </c>
-      <c r="AB12" s="97" t="s">
+      <c r="AB12" s="86" t="s">
         <v>70</v>
       </c>
-      <c r="AC12" s="97" t="s">
+      <c r="AC12" s="86" t="s">
         <v>71</v>
       </c>
-      <c r="AD12" s="97" t="s">
+      <c r="AD12" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="AE12" s="97" t="s">
+      <c r="AE12" s="86" t="s">
         <v>73</v>
       </c>
-      <c r="AF12" s="97"/>
+      <c r="AF12" s="86"/>
     </row>
     <row r="13" spans="2:32" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="41">
+      <c r="C13" s="40">
         <v>18</v>
       </c>
-      <c r="D13" s="42"/>
-      <c r="E13" s="41">
+      <c r="D13" s="41"/>
+      <c r="E13" s="40">
         <v>11</v>
       </c>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53">
+      <c r="F13" s="52"/>
+      <c r="G13" s="52">
         <v>6</v>
       </c>
-      <c r="H13" s="54">
+      <c r="H13" s="53">
         <v>1694.84</v>
       </c>
-      <c r="I13" s="43"/>
-      <c r="J13" s="55">
+      <c r="I13" s="42"/>
+      <c r="J13" s="54">
         <v>25.88</v>
       </c>
-      <c r="K13" s="56">
+      <c r="K13" s="55">
         <v>6.58</v>
       </c>
-      <c r="L13" s="57">
+      <c r="L13" s="56">
         <v>13.08</v>
       </c>
-      <c r="M13" s="57">
+      <c r="M13" s="56">
         <v>2.25</v>
       </c>
-      <c r="N13" s="57">
+      <c r="N13" s="56">
         <v>0.08</v>
       </c>
-      <c r="O13" s="99"/>
+      <c r="O13" s="88"/>
       <c r="P13" s="1">
         <f>H13/L13</f>
         <v>129.5749235474006</v>
@@ -4162,43 +4151,43 @@
         <f>(H13*SUM(J13:N13)/SUM(K13:N13))/(100*100)/(1.016*1)</f>
         <v>0.36313925263093816</v>
       </c>
-      <c r="AF13" s="98"/>
+      <c r="AF13" s="87"/>
     </row>
     <row r="14" spans="2:32" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="41">
+      <c r="C14" s="40">
         <v>15</v>
       </c>
-      <c r="D14" s="42"/>
-      <c r="E14" s="41">
+      <c r="D14" s="41"/>
+      <c r="E14" s="40">
         <v>13</v>
       </c>
-      <c r="F14" s="53"/>
-      <c r="G14" s="53">
+      <c r="F14" s="52"/>
+      <c r="G14" s="52">
         <v>6</v>
       </c>
-      <c r="H14" s="54">
+      <c r="H14" s="53">
         <v>1841.36</v>
       </c>
-      <c r="I14" s="43"/>
-      <c r="J14" s="55">
+      <c r="I14" s="42"/>
+      <c r="J14" s="54">
         <v>20.239999999999998</v>
       </c>
-      <c r="K14" s="56">
+      <c r="K14" s="55">
         <v>7.06</v>
       </c>
-      <c r="L14" s="57">
+      <c r="L14" s="56">
         <v>13.95</v>
       </c>
-      <c r="M14" s="57">
+      <c r="M14" s="56">
         <v>2.54</v>
       </c>
-      <c r="N14" s="57">
+      <c r="N14" s="56">
         <v>0.09</v>
       </c>
-      <c r="O14" s="99"/>
+      <c r="O14" s="88"/>
       <c r="P14" s="1">
         <f t="shared" ref="P14:P20" si="0">H14/L14</f>
         <v>131.99713261648745</v>
@@ -4260,43 +4249,43 @@
         <f t="shared" ref="AE14:AE20" si="12">(H14*SUM(J14:N14)/SUM(K14:N14))/(100*100)/(1.016*1)</f>
         <v>0.33640631786508923</v>
       </c>
-      <c r="AF14" s="98"/>
+      <c r="AF14" s="87"/>
     </row>
     <row r="15" spans="2:32" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="41">
+      <c r="C15" s="40">
         <v>23</v>
       </c>
-      <c r="D15" s="42"/>
-      <c r="E15" s="41">
+      <c r="D15" s="41"/>
+      <c r="E15" s="40">
         <v>7</v>
       </c>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53">
+      <c r="F15" s="52"/>
+      <c r="G15" s="52">
         <v>6</v>
       </c>
-      <c r="H15" s="54">
+      <c r="H15" s="53">
         <v>1502.55</v>
       </c>
-      <c r="I15" s="43"/>
-      <c r="J15" s="55">
+      <c r="I15" s="42"/>
+      <c r="J15" s="54">
         <v>33.79</v>
       </c>
-      <c r="K15" s="56">
+      <c r="K15" s="55">
         <v>5.71</v>
       </c>
-      <c r="L15" s="57">
+      <c r="L15" s="56">
         <v>11.18</v>
       </c>
-      <c r="M15" s="57">
+      <c r="M15" s="56">
         <v>1.92</v>
       </c>
-      <c r="N15" s="57">
+      <c r="N15" s="56">
         <v>0.02</v>
       </c>
-      <c r="O15" s="99"/>
+      <c r="O15" s="88"/>
       <c r="P15" s="1">
         <f t="shared" si="0"/>
         <v>134.39624329159213</v>
@@ -4358,43 +4347,43 @@
         <f t="shared" si="12"/>
         <v>0.41327177794690162</v>
       </c>
-      <c r="AF15" s="98"/>
+      <c r="AF15" s="87"/>
     </row>
     <row r="16" spans="2:32" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="41">
+      <c r="C16" s="40">
         <v>19</v>
       </c>
-      <c r="D16" s="42"/>
-      <c r="E16" s="41">
+      <c r="D16" s="41"/>
+      <c r="E16" s="40">
         <v>11</v>
       </c>
-      <c r="F16" s="53"/>
-      <c r="G16" s="53">
+      <c r="F16" s="52"/>
+      <c r="G16" s="52">
         <v>5</v>
       </c>
-      <c r="H16" s="54">
+      <c r="H16" s="53">
         <v>1608.36</v>
       </c>
-      <c r="I16" s="43"/>
-      <c r="J16" s="55">
+      <c r="I16" s="42"/>
+      <c r="J16" s="54">
         <v>22.37</v>
       </c>
-      <c r="K16" s="56">
+      <c r="K16" s="55">
         <v>5.5</v>
       </c>
-      <c r="L16" s="57">
+      <c r="L16" s="56">
         <v>11.61</v>
       </c>
-      <c r="M16" s="57">
+      <c r="M16" s="56">
         <v>1.92</v>
       </c>
-      <c r="N16" s="57">
+      <c r="N16" s="56">
         <v>0.08</v>
       </c>
-      <c r="O16" s="99"/>
+      <c r="O16" s="88"/>
       <c r="P16" s="1">
         <f t="shared" si="0"/>
         <v>138.53229974160206</v>
@@ -4456,43 +4445,43 @@
         <f t="shared" si="12"/>
         <v>0.34361144142696454</v>
       </c>
-      <c r="AF16" s="98"/>
+      <c r="AF16" s="87"/>
     </row>
     <row r="17" spans="2:32" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="41">
+      <c r="C17" s="40">
         <v>18</v>
       </c>
-      <c r="D17" s="42"/>
-      <c r="E17" s="41">
+      <c r="D17" s="41"/>
+      <c r="E17" s="40">
         <v>9</v>
       </c>
-      <c r="F17" s="53"/>
-      <c r="G17" s="53">
+      <c r="F17" s="52"/>
+      <c r="G17" s="52">
         <v>5</v>
       </c>
-      <c r="H17" s="54">
+      <c r="H17" s="53">
         <v>1672.87</v>
       </c>
-      <c r="I17" s="43"/>
-      <c r="J17" s="55">
+      <c r="I17" s="42"/>
+      <c r="J17" s="54">
         <v>24.19</v>
       </c>
-      <c r="K17" s="56">
+      <c r="K17" s="55">
         <v>6.01</v>
       </c>
-      <c r="L17" s="57">
+      <c r="L17" s="56">
         <v>13.26</v>
       </c>
-      <c r="M17" s="57">
+      <c r="M17" s="56">
         <v>2.2799999999999998</v>
       </c>
-      <c r="N17" s="57">
+      <c r="N17" s="56">
         <v>0.05</v>
       </c>
-      <c r="O17" s="99"/>
+      <c r="O17" s="88"/>
       <c r="P17" s="1">
         <f t="shared" si="0"/>
         <v>126.15912518853695</v>
@@ -4554,43 +4543,43 @@
         <f t="shared" si="12"/>
         <v>0.34904817958953038</v>
       </c>
-      <c r="AF17" s="98"/>
+      <c r="AF17" s="87"/>
     </row>
     <row r="18" spans="2:32" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="41">
+      <c r="C18" s="40">
         <v>21</v>
       </c>
-      <c r="D18" s="42"/>
-      <c r="E18" s="41">
+      <c r="D18" s="41"/>
+      <c r="E18" s="40">
         <v>11</v>
       </c>
-      <c r="F18" s="53"/>
-      <c r="G18" s="53">
+      <c r="F18" s="52"/>
+      <c r="G18" s="52">
         <v>5</v>
       </c>
-      <c r="H18" s="54">
+      <c r="H18" s="53">
         <v>1471.61</v>
       </c>
-      <c r="I18" s="43"/>
-      <c r="J18" s="55">
+      <c r="I18" s="42"/>
+      <c r="J18" s="54">
         <v>28.38</v>
       </c>
-      <c r="K18" s="56">
+      <c r="K18" s="55">
         <v>5.82</v>
       </c>
-      <c r="L18" s="57">
+      <c r="L18" s="56">
         <v>10.83</v>
       </c>
-      <c r="M18" s="57">
+      <c r="M18" s="56">
         <v>2.17</v>
       </c>
-      <c r="N18" s="57">
+      <c r="N18" s="56">
         <v>0.08</v>
       </c>
-      <c r="O18" s="99"/>
+      <c r="O18" s="88"/>
       <c r="P18" s="1">
         <f t="shared" si="0"/>
         <v>135.88273314866112</v>
@@ -4652,43 +4641,43 @@
         <f t="shared" si="12"/>
         <v>0.36233867016622923</v>
       </c>
-      <c r="AF18" s="98"/>
+      <c r="AF18" s="87"/>
     </row>
     <row r="19" spans="2:32" s="4" customFormat="1" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="41">
+      <c r="C19" s="40">
         <v>20</v>
       </c>
-      <c r="D19" s="42"/>
-      <c r="E19" s="41">
+      <c r="D19" s="41"/>
+      <c r="E19" s="40">
         <v>8</v>
       </c>
-      <c r="F19" s="53"/>
-      <c r="G19" s="53">
+      <c r="F19" s="52"/>
+      <c r="G19" s="52">
         <v>7</v>
       </c>
-      <c r="H19" s="54">
+      <c r="H19" s="53">
         <v>1625.6</v>
       </c>
-      <c r="I19" s="43"/>
-      <c r="J19" s="55">
+      <c r="I19" s="42"/>
+      <c r="J19" s="54">
         <v>31.92</v>
       </c>
-      <c r="K19" s="56">
+      <c r="K19" s="55">
         <v>5.63</v>
       </c>
-      <c r="L19" s="57">
+      <c r="L19" s="56">
         <v>12.06</v>
       </c>
-      <c r="M19" s="57">
+      <c r="M19" s="56">
         <v>1.99</v>
       </c>
-      <c r="N19" s="57">
+      <c r="N19" s="56">
         <v>0.04</v>
       </c>
-      <c r="O19" s="99"/>
+      <c r="O19" s="88"/>
       <c r="P19" s="1">
         <f t="shared" si="0"/>
         <v>134.7927031509121</v>
@@ -4750,43 +4739,43 @@
         <f t="shared" si="12"/>
         <v>0.4189858012170386</v>
       </c>
-      <c r="AF19" s="98"/>
+      <c r="AF19" s="87"/>
     </row>
     <row r="20" spans="2:32" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="41">
+      <c r="C20" s="40">
         <v>17</v>
       </c>
-      <c r="D20" s="42"/>
-      <c r="E20" s="41">
+      <c r="D20" s="41"/>
+      <c r="E20" s="40">
         <v>5</v>
       </c>
-      <c r="F20" s="53"/>
-      <c r="G20" s="53">
+      <c r="F20" s="52"/>
+      <c r="G20" s="52">
         <v>5</v>
       </c>
-      <c r="H20" s="54">
+      <c r="H20" s="53">
         <v>1804.25</v>
       </c>
-      <c r="I20" s="43"/>
-      <c r="J20" s="55">
+      <c r="I20" s="42"/>
+      <c r="J20" s="54">
         <v>25.89</v>
       </c>
-      <c r="K20" s="56">
+      <c r="K20" s="55">
         <v>7.27</v>
       </c>
-      <c r="L20" s="57">
+      <c r="L20" s="56">
         <v>13.4</v>
       </c>
-      <c r="M20" s="57">
+      <c r="M20" s="56">
         <v>2.4</v>
       </c>
-      <c r="N20" s="57">
+      <c r="N20" s="56">
         <v>0.04</v>
       </c>
-      <c r="O20" s="99"/>
+      <c r="O20" s="88"/>
       <c r="P20" s="1">
         <f t="shared" si="0"/>
         <v>134.6455223880597</v>
@@ -4848,7 +4837,7 @@
         <f t="shared" si="12"/>
         <v>0.37652961529419376</v>
       </c>
-      <c r="AF20" s="98"/>
+      <c r="AF20" s="87"/>
     </row>
     <row r="21" spans="2:32" ht="29.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C21" s="1">
@@ -4872,7 +4861,7 @@
     <row r="23" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="2:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="N25" s="87">
+      <c r="N25" s="85">
         <f>AVERAGE(N13:N20)</f>
         <v>5.9999999999999991E-2</v>
       </c>
@@ -4980,10 +4969,10 @@
       <c r="D5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>40724</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D6" s="5" t="s">
@@ -5001,11 +4990,11 @@
       <c r="E8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="9"/>
+      <c r="F8" s="8"/>
       <c r="K8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L8" s="69">
+      <c r="L8" s="68">
         <v>40731</v>
       </c>
     </row>
@@ -5020,165 +5009,161 @@
     </row>
     <row r="10" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="5"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
     </row>
     <row r="11" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D11" s="8"/>
-      <c r="E11" s="10" t="s">
+      <c r="D11" s="7"/>
+      <c r="E11" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
     </row>
     <row r="12" spans="1:34" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="13" t="s">
+      <c r="D12" s="13"/>
+      <c r="E12" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="H12" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="I12" s="14"/>
-      <c r="J12" s="15" t="s">
+      <c r="I12" s="13"/>
+      <c r="J12" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="K12" s="22" t="s">
+      <c r="K12" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="L12" s="22" t="s">
+      <c r="L12" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M12" s="23" t="s">
+      <c r="M12" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="N12" s="13" t="s">
+      <c r="N12" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="O12" s="13" t="s">
+      <c r="O12" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="15" t="s">
+      <c r="P12" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="Q12" s="25" t="s">
+      <c r="Q12" s="24" t="s">
         <v>34</v>
       </c>
       <c r="V12" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="W12" s="97" t="s">
+      <c r="W12" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="X12" s="97" t="s">
+      <c r="X12" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="Y12" s="97" t="s">
+      <c r="Y12" s="86" t="s">
         <v>74</v>
       </c>
-      <c r="Z12" s="97" t="s">
+      <c r="Z12" s="86" t="s">
         <v>75</v>
       </c>
-      <c r="AA12" s="97" t="s">
+      <c r="AA12" s="86" t="s">
         <v>66</v>
       </c>
-      <c r="AB12" s="97" t="s">
+      <c r="AB12" s="86" t="s">
         <v>67</v>
       </c>
-      <c r="AC12" s="97" t="s">
+      <c r="AC12" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="AD12" s="97" t="s">
+      <c r="AD12" s="86" t="s">
         <v>69</v>
       </c>
-      <c r="AE12" s="97" t="s">
+      <c r="AE12" s="86" t="s">
         <v>70</v>
       </c>
-      <c r="AF12" s="97" t="s">
+      <c r="AF12" s="86" t="s">
         <v>71</v>
       </c>
-      <c r="AG12" s="97" t="s">
+      <c r="AG12" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="AH12" s="97" t="s">
+      <c r="AH12" s="86" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:34" ht="40.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="88" t="s">
+      <c r="A13" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="40">
+      <c r="B13" s="39">
         <v>2</v>
       </c>
-      <c r="C13" s="41">
+      <c r="C13" s="40">
         <v>14</v>
       </c>
-      <c r="D13" s="42"/>
-      <c r="E13" s="41">
+      <c r="D13" s="41"/>
+      <c r="E13" s="40">
         <v>160</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="40">
         <v>5</v>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="40">
         <v>9</v>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="40">
         <v>16802</v>
       </c>
-      <c r="I13" s="43"/>
-      <c r="J13" s="44"/>
-      <c r="K13" s="45">
+      <c r="I13" s="42"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="44">
         <v>265.58999999999997</v>
       </c>
-      <c r="L13" s="70">
+      <c r="L13" s="69">
         <v>68.98</v>
       </c>
-      <c r="M13" s="46">
+      <c r="M13" s="45">
         <f>K13-L13</f>
         <v>196.60999999999996</v>
       </c>
-      <c r="N13" s="47">
+      <c r="N13" s="46">
         <v>103.42</v>
       </c>
-      <c r="O13" s="48">
+      <c r="O13" s="47">
         <v>102.63</v>
       </c>
-      <c r="P13" s="48">
+      <c r="P13" s="47">
         <v>23.39</v>
       </c>
-      <c r="Q13" s="48">
+      <c r="Q13" s="47">
         <v>16.059999999999999</v>
       </c>
       <c r="S13" s="1">
@@ -5246,48 +5231,48 @@
       </c>
     </row>
     <row r="14" spans="1:34" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="89"/>
-      <c r="B14" s="40">
+      <c r="A14" s="93"/>
+      <c r="B14" s="39">
         <v>4</v>
       </c>
-      <c r="C14" s="41">
+      <c r="C14" s="40">
         <v>17</v>
       </c>
-      <c r="D14" s="42"/>
-      <c r="E14" s="41">
+      <c r="D14" s="41"/>
+      <c r="E14" s="40">
         <v>127</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="40">
         <v>3</v>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="40">
         <v>21</v>
       </c>
-      <c r="H14" s="41">
+      <c r="H14" s="40">
         <v>15368</v>
       </c>
-      <c r="I14" s="43"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="49">
+      <c r="I14" s="42"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="48">
         <v>318.85000000000002</v>
       </c>
-      <c r="L14" s="71">
+      <c r="L14" s="70">
         <v>69.38</v>
       </c>
-      <c r="M14" s="50">
+      <c r="M14" s="49">
         <f t="shared" ref="M14:M20" si="0">K14-L14</f>
         <v>249.47000000000003</v>
       </c>
-      <c r="N14" s="47">
+      <c r="N14" s="46">
         <v>91.26</v>
       </c>
-      <c r="O14" s="48">
+      <c r="O14" s="47">
         <v>94.11</v>
       </c>
-      <c r="P14" s="48">
+      <c r="P14" s="47">
         <v>21.98</v>
       </c>
-      <c r="Q14" s="48">
+      <c r="Q14" s="47">
         <v>16.739999999999998</v>
       </c>
       <c r="S14" s="1">
@@ -5355,48 +5340,48 @@
       </c>
     </row>
     <row r="15" spans="1:34" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="89"/>
-      <c r="B15" s="40">
+      <c r="A15" s="93"/>
+      <c r="B15" s="39">
         <v>6</v>
       </c>
-      <c r="C15" s="41">
+      <c r="C15" s="40">
         <v>22</v>
       </c>
-      <c r="D15" s="42"/>
-      <c r="E15" s="41">
+      <c r="D15" s="41"/>
+      <c r="E15" s="40">
         <v>89</v>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="40">
         <v>3</v>
       </c>
-      <c r="G15" s="41">
+      <c r="G15" s="40">
         <v>15</v>
       </c>
-      <c r="H15" s="41">
+      <c r="H15" s="40">
         <v>9038</v>
       </c>
-      <c r="I15" s="43"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="49">
+      <c r="I15" s="42"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="48">
         <v>321.67</v>
       </c>
-      <c r="L15" s="71">
+      <c r="L15" s="70">
         <v>69.25</v>
       </c>
-      <c r="M15" s="50">
+      <c r="M15" s="49">
         <f t="shared" si="0"/>
         <v>252.42000000000002</v>
       </c>
-      <c r="N15" s="47">
+      <c r="N15" s="46">
         <v>61.77</v>
       </c>
-      <c r="O15" s="48">
+      <c r="O15" s="47">
         <v>63.24</v>
       </c>
-      <c r="P15" s="48">
+      <c r="P15" s="47">
         <v>13.49</v>
       </c>
-      <c r="Q15" s="48">
+      <c r="Q15" s="47">
         <v>12.34</v>
       </c>
       <c r="S15" s="1">
@@ -5464,48 +5449,48 @@
       </c>
     </row>
     <row r="16" spans="1:34" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="89"/>
-      <c r="B16" s="40">
+      <c r="A16" s="93"/>
+      <c r="B16" s="39">
         <v>8</v>
       </c>
-      <c r="C16" s="41">
+      <c r="C16" s="40">
         <v>19</v>
       </c>
-      <c r="D16" s="42"/>
-      <c r="E16" s="41">
+      <c r="D16" s="41"/>
+      <c r="E16" s="40">
         <v>139</v>
       </c>
-      <c r="F16" s="41">
+      <c r="F16" s="40">
         <v>3</v>
       </c>
-      <c r="G16" s="41">
+      <c r="G16" s="40">
         <v>27</v>
       </c>
-      <c r="H16" s="41">
+      <c r="H16" s="40">
         <v>15080</v>
       </c>
-      <c r="I16" s="43"/>
-      <c r="J16" s="44"/>
-      <c r="K16" s="49">
+      <c r="I16" s="42"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="48">
         <v>318.60000000000002</v>
       </c>
-      <c r="L16" s="71">
+      <c r="L16" s="70">
         <v>69.81</v>
       </c>
-      <c r="M16" s="50">
+      <c r="M16" s="49">
         <f t="shared" si="0"/>
         <v>248.79000000000002</v>
       </c>
-      <c r="N16" s="47">
+      <c r="N16" s="46">
         <v>88.35</v>
       </c>
-      <c r="O16" s="48">
+      <c r="O16" s="47">
         <v>87.22</v>
       </c>
-      <c r="P16" s="48">
+      <c r="P16" s="47">
         <v>20.23</v>
       </c>
-      <c r="Q16" s="48">
+      <c r="Q16" s="47">
         <v>19.97</v>
       </c>
       <c r="S16" s="1">
@@ -5573,48 +5558,48 @@
       </c>
     </row>
     <row r="17" spans="1:34" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="90"/>
-      <c r="B17" s="40">
+      <c r="A17" s="94"/>
+      <c r="B17" s="39">
         <v>9</v>
       </c>
-      <c r="C17" s="41">
+      <c r="C17" s="40">
         <v>21</v>
       </c>
-      <c r="D17" s="42"/>
-      <c r="E17" s="41">
+      <c r="D17" s="41"/>
+      <c r="E17" s="40">
         <v>95</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="40">
         <v>4</v>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="40">
         <v>18</v>
       </c>
-      <c r="H17" s="41">
+      <c r="H17" s="40">
         <v>9346</v>
       </c>
-      <c r="I17" s="43"/>
-      <c r="J17" s="44"/>
-      <c r="K17" s="49">
+      <c r="I17" s="42"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="48">
         <v>291.49</v>
       </c>
-      <c r="L17" s="71">
+      <c r="L17" s="70">
         <v>69.86</v>
       </c>
-      <c r="M17" s="50">
+      <c r="M17" s="49">
         <f t="shared" si="0"/>
         <v>221.63</v>
       </c>
-      <c r="N17" s="47">
+      <c r="N17" s="46">
         <v>58.66</v>
       </c>
-      <c r="O17" s="48">
+      <c r="O17" s="47">
         <v>63.19</v>
       </c>
-      <c r="P17" s="48">
+      <c r="P17" s="47">
         <v>13.08</v>
       </c>
-      <c r="Q17" s="48">
+      <c r="Q17" s="47">
         <v>14.72</v>
       </c>
       <c r="S17" s="1">
@@ -5682,50 +5667,50 @@
       </c>
     </row>
     <row r="18" spans="1:34" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="91" t="s">
+      <c r="A18" s="95" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="40">
+      <c r="B18" s="39">
         <v>11</v>
       </c>
-      <c r="C18" s="41">
+      <c r="C18" s="40">
         <v>17</v>
       </c>
-      <c r="D18" s="42"/>
-      <c r="E18" s="41">
+      <c r="D18" s="41"/>
+      <c r="E18" s="40">
         <v>130</v>
       </c>
-      <c r="F18" s="41">
+      <c r="F18" s="40">
         <v>7</v>
       </c>
-      <c r="G18" s="41">
+      <c r="G18" s="40">
         <v>25</v>
       </c>
-      <c r="H18" s="41">
+      <c r="H18" s="40">
         <v>11651</v>
       </c>
-      <c r="I18" s="43"/>
-      <c r="J18" s="44"/>
-      <c r="K18" s="49">
+      <c r="I18" s="42"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="48">
         <v>241.16</v>
       </c>
-      <c r="L18" s="71">
+      <c r="L18" s="70">
         <v>69.31</v>
       </c>
-      <c r="M18" s="50">
+      <c r="M18" s="49">
         <f t="shared" si="0"/>
         <v>171.85</v>
       </c>
-      <c r="N18" s="47">
+      <c r="N18" s="46">
         <v>80.680000000000007</v>
       </c>
-      <c r="O18" s="48">
+      <c r="O18" s="47">
         <v>82.04</v>
       </c>
-      <c r="P18" s="48">
+      <c r="P18" s="47">
         <v>16.68</v>
       </c>
-      <c r="Q18" s="48">
+      <c r="Q18" s="47">
         <v>26.69</v>
       </c>
       <c r="S18" s="1">
@@ -5793,48 +5778,48 @@
       </c>
     </row>
     <row r="19" spans="1:34" s="4" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="92"/>
-      <c r="B19" s="40">
+      <c r="A19" s="96"/>
+      <c r="B19" s="39">
         <v>14</v>
       </c>
-      <c r="C19" s="41">
+      <c r="C19" s="40">
         <v>17</v>
       </c>
-      <c r="D19" s="42"/>
-      <c r="E19" s="41">
+      <c r="D19" s="41"/>
+      <c r="E19" s="40">
         <v>102</v>
       </c>
-      <c r="F19" s="41">
+      <c r="F19" s="40">
         <v>3</v>
       </c>
-      <c r="G19" s="41">
+      <c r="G19" s="40">
         <v>28</v>
       </c>
-      <c r="H19" s="41">
+      <c r="H19" s="40">
         <v>14912</v>
       </c>
-      <c r="I19" s="43"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="49">
+      <c r="I19" s="42"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="48">
         <v>292.06</v>
       </c>
-      <c r="L19" s="71">
+      <c r="L19" s="70">
         <v>70.069999999999993</v>
       </c>
-      <c r="M19" s="50">
+      <c r="M19" s="49">
         <f t="shared" si="0"/>
         <v>221.99</v>
       </c>
-      <c r="N19" s="47">
+      <c r="N19" s="46">
         <v>87.84</v>
       </c>
-      <c r="O19" s="48">
+      <c r="O19" s="47">
         <v>89.67</v>
       </c>
-      <c r="P19" s="48">
+      <c r="P19" s="47">
         <v>19.7</v>
       </c>
-      <c r="Q19" s="48">
+      <c r="Q19" s="47">
         <v>21.08</v>
       </c>
       <c r="R19" s="2"/>
@@ -5903,48 +5888,48 @@
       </c>
     </row>
     <row r="20" spans="1:34" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="93"/>
-      <c r="B20" s="40">
+      <c r="A20" s="97"/>
+      <c r="B20" s="39">
         <v>15</v>
       </c>
-      <c r="C20" s="41">
+      <c r="C20" s="40">
         <v>17</v>
       </c>
-      <c r="D20" s="42"/>
-      <c r="E20" s="41">
+      <c r="D20" s="41"/>
+      <c r="E20" s="40">
         <v>105</v>
       </c>
-      <c r="F20" s="41">
+      <c r="F20" s="40">
         <v>5</v>
       </c>
-      <c r="G20" s="41">
+      <c r="G20" s="40">
         <v>19</v>
       </c>
-      <c r="H20" s="41">
+      <c r="H20" s="40">
         <v>13436</v>
       </c>
-      <c r="I20" s="43"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="51">
+      <c r="I20" s="42"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="50">
         <v>292.05</v>
       </c>
-      <c r="L20" s="72">
+      <c r="L20" s="71">
         <v>70.180000000000007</v>
       </c>
-      <c r="M20" s="52">
+      <c r="M20" s="51">
         <f t="shared" si="0"/>
         <v>221.87</v>
       </c>
-      <c r="N20" s="47">
+      <c r="N20" s="46">
         <v>81.459999999999994</v>
       </c>
-      <c r="O20" s="48">
+      <c r="O20" s="47">
         <v>83.86</v>
       </c>
-      <c r="P20" s="48">
+      <c r="P20" s="47">
         <v>16.98</v>
       </c>
-      <c r="Q20" s="48">
+      <c r="Q20" s="47">
         <v>17.420000000000002</v>
       </c>
       <c r="S20" s="1">
@@ -6012,7 +5997,7 @@
       </c>
     </row>
     <row r="21" spans="1:34" ht="29.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="39"/>
+      <c r="A21" s="38"/>
       <c r="C21" s="1">
         <f>AVERAGE(C13:C20)</f>
         <v>18</v>
@@ -6035,7 +6020,7 @@
     <row r="24" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q26" s="87">
+      <c r="Q26" s="85">
         <f>AVERAGE(Q13:Q20)</f>
         <v>18.127499999999998</v>
       </c>
@@ -6149,260 +6134,248 @@
       </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="B5" s="30"/>
-      <c r="C5" s="30" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="29" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="6"/>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="24"/>
-      <c r="G5" s="7"/>
+      <c r="F5" s="23"/>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="B6" s="30"/>
-      <c r="C6" s="30" t="s">
+      <c r="B6" s="29"/>
+      <c r="C6" s="29" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
     </row>
     <row r="8" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="30"/>
-      <c r="C8" s="30" t="s">
+      <c r="B8" s="29"/>
+      <c r="C8" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="6"/>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="24"/>
-      <c r="G8" s="7"/>
+      <c r="F8" s="23"/>
       <c r="K8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L8" s="9">
+      <c r="L8" s="8">
         <v>40764</v>
       </c>
-      <c r="M8" s="24"/>
+      <c r="M8" s="23"/>
     </row>
     <row r="9" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="30"/>
-      <c r="C9" s="30" t="s">
+      <c r="B9" s="29"/>
+      <c r="C9" s="29" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="5"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15"/>
+      <c r="R10" s="15"/>
     </row>
     <row r="11" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D11" s="8"/>
-      <c r="E11" s="10" t="s">
+      <c r="D11" s="7"/>
+      <c r="E11" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="73"/>
-      <c r="K11" s="73"/>
-      <c r="L11" s="74"/>
-      <c r="M11" s="74"/>
-      <c r="N11" s="75"/>
-      <c r="O11" s="75"/>
-      <c r="P11" s="75"/>
-      <c r="Q11" s="75"/>
-      <c r="R11" s="75"/>
-      <c r="S11" s="76"/>
-      <c r="T11" s="76"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="72"/>
+      <c r="K11" s="72"/>
+      <c r="L11" s="73"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="74"/>
+      <c r="P11" s="74"/>
+      <c r="Q11" s="74"/>
+      <c r="R11" s="74"/>
     </row>
     <row r="12" spans="1:37" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="13" t="s">
+      <c r="D12" s="13"/>
+      <c r="E12" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="H12" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I12" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="32" t="s">
+      <c r="J12" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="K12" s="33" t="s">
+      <c r="K12" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="L12" s="34" t="s">
+      <c r="L12" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="M12" s="32" t="s">
+      <c r="M12" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="N12" s="33" t="s">
+      <c r="N12" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="O12" s="34" t="s">
+      <c r="O12" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="P12" s="32" t="s">
+      <c r="P12" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="Q12" s="33" t="s">
+      <c r="Q12" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="R12" s="34" t="s">
+      <c r="R12" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="S12" s="35" t="s">
+      <c r="S12" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="T12" s="36" t="s">
+      <c r="T12" s="35" t="s">
         <v>39</v>
       </c>
       <c r="Y12" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="Z12" s="97" t="s">
+      <c r="Z12" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="AA12" s="97" t="s">
+      <c r="AA12" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="AB12" s="97" t="s">
+      <c r="AB12" s="86" t="s">
         <v>74</v>
       </c>
-      <c r="AC12" s="97" t="s">
+      <c r="AC12" s="86" t="s">
         <v>75</v>
       </c>
-      <c r="AD12" s="97" t="s">
+      <c r="AD12" s="86" t="s">
         <v>66</v>
       </c>
-      <c r="AE12" s="97" t="s">
+      <c r="AE12" s="86" t="s">
         <v>67</v>
       </c>
-      <c r="AF12" s="97" t="s">
+      <c r="AF12" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="AG12" s="97" t="s">
+      <c r="AG12" s="86" t="s">
         <v>69</v>
       </c>
-      <c r="AH12" s="97" t="s">
+      <c r="AH12" s="86" t="s">
         <v>70</v>
       </c>
-      <c r="AI12" s="97" t="s">
+      <c r="AI12" s="86" t="s">
         <v>71</v>
       </c>
-      <c r="AJ12" s="97" t="s">
+      <c r="AJ12" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="AK12" s="97" t="s">
+      <c r="AK12" s="86" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:37" ht="40.15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="77" t="s">
+      <c r="A13" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="25">
         <v>1</v>
       </c>
-      <c r="C13" s="41">
+      <c r="C13" s="40">
         <v>16</v>
       </c>
-      <c r="D13" s="42"/>
-      <c r="E13" s="41">
+      <c r="D13" s="41"/>
+      <c r="E13" s="40">
         <v>26</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="40">
         <v>3</v>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="40">
         <v>52</v>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="40">
         <v>16894</v>
       </c>
-      <c r="I13" s="79" t="s">
+      <c r="I13" s="77" t="s">
         <v>54</v>
       </c>
-      <c r="J13" s="58">
+      <c r="J13" s="57">
         <v>521.08000000000004</v>
       </c>
-      <c r="K13" s="59">
+      <c r="K13" s="58">
         <v>62.95</v>
       </c>
-      <c r="L13" s="60">
+      <c r="L13" s="59">
         <f>J13-K13</f>
         <v>458.13000000000005</v>
       </c>
-      <c r="M13" s="58">
+      <c r="M13" s="57">
         <v>124.41</v>
       </c>
-      <c r="N13" s="59">
+      <c r="N13" s="58">
         <v>16.670000000000002</v>
       </c>
-      <c r="O13" s="60">
+      <c r="O13" s="59">
         <f t="shared" ref="O13:O20" si="0">M13-N13</f>
         <v>107.74</v>
       </c>
-      <c r="P13" s="58">
+      <c r="P13" s="57">
         <v>119.41</v>
       </c>
-      <c r="Q13" s="59">
+      <c r="Q13" s="58">
         <v>16.73</v>
       </c>
-      <c r="R13" s="60">
+      <c r="R13" s="59">
         <f t="shared" ref="R13:R20" si="1">P13-Q13</f>
         <v>102.67999999999999</v>
       </c>
-      <c r="S13" s="61">
+      <c r="S13" s="60">
         <v>19.22</v>
       </c>
-      <c r="T13" s="62">
+      <c r="T13" s="61">
         <v>127.22</v>
       </c>
       <c r="V13" s="1">
@@ -6470,63 +6443,63 @@
       </c>
     </row>
     <row r="14" spans="1:37" ht="40.15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="77" t="s">
+      <c r="A14" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="25">
         <v>3</v>
       </c>
-      <c r="C14" s="41">
+      <c r="C14" s="40">
         <v>19</v>
       </c>
-      <c r="D14" s="42"/>
-      <c r="E14" s="41">
+      <c r="D14" s="41"/>
+      <c r="E14" s="40">
         <v>13</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="40">
         <v>1</v>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="40">
         <v>54</v>
       </c>
-      <c r="H14" s="41">
+      <c r="H14" s="40">
         <v>17115</v>
       </c>
-      <c r="I14" s="79"/>
-      <c r="J14" s="63">
+      <c r="I14" s="77"/>
+      <c r="J14" s="62">
         <v>553.30999999999995</v>
       </c>
-      <c r="K14" s="48">
+      <c r="K14" s="47">
         <v>77.02</v>
       </c>
-      <c r="L14" s="60">
+      <c r="L14" s="59">
         <f t="shared" ref="L14:L20" si="2">J14-K14</f>
         <v>476.28999999999996</v>
       </c>
-      <c r="M14" s="63">
+      <c r="M14" s="62">
         <v>108.28</v>
       </c>
-      <c r="N14" s="48">
+      <c r="N14" s="47">
         <v>16.68</v>
       </c>
-      <c r="O14" s="60">
+      <c r="O14" s="59">
         <f t="shared" si="0"/>
         <v>91.6</v>
       </c>
-      <c r="P14" s="63">
+      <c r="P14" s="62">
         <v>134.57</v>
       </c>
-      <c r="Q14" s="48">
+      <c r="Q14" s="47">
         <v>31.78</v>
       </c>
-      <c r="R14" s="60">
+      <c r="R14" s="59">
         <f t="shared" si="1"/>
         <v>102.78999999999999</v>
       </c>
-      <c r="S14" s="64">
+      <c r="S14" s="63">
         <v>18.86</v>
       </c>
-      <c r="T14" s="65">
+      <c r="T14" s="64">
         <v>129.25</v>
       </c>
       <c r="V14" s="1">
@@ -6594,63 +6567,63 @@
       </c>
     </row>
     <row r="15" spans="1:37" ht="40.15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="77" t="s">
+      <c r="A15" s="75" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="25">
         <v>5</v>
       </c>
-      <c r="C15" s="41">
+      <c r="C15" s="40">
         <v>18</v>
       </c>
-      <c r="D15" s="42"/>
-      <c r="E15" s="41">
+      <c r="D15" s="41"/>
+      <c r="E15" s="40">
         <v>20</v>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="40">
         <v>1</v>
       </c>
-      <c r="G15" s="41">
+      <c r="G15" s="40">
         <v>71</v>
       </c>
-      <c r="H15" s="41">
+      <c r="H15" s="40">
         <v>18602</v>
       </c>
-      <c r="I15" s="79"/>
-      <c r="J15" s="63">
+      <c r="I15" s="77"/>
+      <c r="J15" s="62">
         <v>520.5</v>
       </c>
-      <c r="K15" s="48">
+      <c r="K15" s="47">
         <v>62.7</v>
       </c>
-      <c r="L15" s="60">
+      <c r="L15" s="59">
         <f t="shared" si="2"/>
         <v>457.8</v>
       </c>
-      <c r="M15" s="63">
+      <c r="M15" s="62">
         <v>128.04</v>
       </c>
-      <c r="N15" s="48">
+      <c r="N15" s="47">
         <v>16.649999999999999</v>
       </c>
-      <c r="O15" s="60">
+      <c r="O15" s="59">
         <f t="shared" si="0"/>
         <v>111.38999999999999</v>
       </c>
-      <c r="P15" s="63">
+      <c r="P15" s="62">
         <v>133.91</v>
       </c>
-      <c r="Q15" s="48">
+      <c r="Q15" s="47">
         <v>31.75</v>
       </c>
-      <c r="R15" s="60">
+      <c r="R15" s="59">
         <f t="shared" si="1"/>
         <v>102.16</v>
       </c>
-      <c r="S15" s="64">
+      <c r="S15" s="63">
         <v>21.64</v>
       </c>
-      <c r="T15" s="65">
+      <c r="T15" s="64">
         <v>136.13999999999999</v>
       </c>
       <c r="V15" s="1">
@@ -6718,63 +6691,63 @@
       </c>
     </row>
     <row r="16" spans="1:37" ht="40.15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="77" t="s">
+      <c r="A16" s="75" t="s">
         <v>53</v>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="25">
         <v>7</v>
       </c>
-      <c r="C16" s="41">
+      <c r="C16" s="40">
         <v>19</v>
       </c>
-      <c r="D16" s="42"/>
-      <c r="E16" s="41">
+      <c r="D16" s="41"/>
+      <c r="E16" s="40">
         <v>31</v>
       </c>
-      <c r="F16" s="41">
+      <c r="F16" s="40">
         <v>2</v>
       </c>
-      <c r="G16" s="41">
+      <c r="G16" s="40">
         <v>67</v>
       </c>
-      <c r="H16" s="41">
+      <c r="H16" s="40">
         <v>21987</v>
       </c>
-      <c r="I16" s="79"/>
-      <c r="J16" s="63">
+      <c r="I16" s="77"/>
+      <c r="J16" s="62">
         <v>729.58</v>
       </c>
-      <c r="K16" s="48">
+      <c r="K16" s="47">
         <v>64.38</v>
       </c>
-      <c r="L16" s="60">
+      <c r="L16" s="59">
         <f t="shared" si="2"/>
         <v>665.2</v>
       </c>
-      <c r="M16" s="63">
+      <c r="M16" s="62">
         <v>138.29</v>
       </c>
-      <c r="N16" s="48">
+      <c r="N16" s="47">
         <v>16.54</v>
       </c>
-      <c r="O16" s="60">
+      <c r="O16" s="59">
         <f t="shared" si="0"/>
         <v>121.75</v>
       </c>
-      <c r="P16" s="63">
+      <c r="P16" s="62">
         <v>150.26</v>
       </c>
-      <c r="Q16" s="48">
+      <c r="Q16" s="47">
         <v>31.54</v>
       </c>
-      <c r="R16" s="60">
+      <c r="R16" s="59">
         <f t="shared" si="1"/>
         <v>118.72</v>
       </c>
-      <c r="S16" s="64">
+      <c r="S16" s="63">
         <v>26.12</v>
       </c>
-      <c r="T16" s="65">
+      <c r="T16" s="64">
         <v>165.35</v>
       </c>
       <c r="V16" s="1">
@@ -6842,65 +6815,65 @@
       </c>
     </row>
     <row r="17" spans="1:38" ht="40.15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="78" t="s">
+      <c r="A17" s="76" t="s">
         <v>52</v>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="25">
         <v>10</v>
       </c>
-      <c r="C17" s="41">
+      <c r="C17" s="40">
         <v>15</v>
       </c>
-      <c r="D17" s="42"/>
-      <c r="E17" s="41">
+      <c r="D17" s="41"/>
+      <c r="E17" s="40">
         <v>88</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="40">
         <v>2</v>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="40">
         <v>73</v>
       </c>
-      <c r="H17" s="41">
+      <c r="H17" s="40">
         <v>29634</v>
       </c>
-      <c r="I17" s="79" t="s">
+      <c r="I17" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="J17" s="63">
+      <c r="J17" s="62">
         <v>554.92999999999995</v>
       </c>
-      <c r="K17" s="48">
+      <c r="K17" s="47">
         <v>68.540000000000006</v>
       </c>
-      <c r="L17" s="60">
+      <c r="L17" s="59">
         <f t="shared" si="2"/>
         <v>486.38999999999993</v>
       </c>
-      <c r="M17" s="63">
+      <c r="M17" s="62">
         <v>204.69</v>
       </c>
-      <c r="N17" s="48">
+      <c r="N17" s="47">
         <v>31.6</v>
       </c>
-      <c r="O17" s="60">
+      <c r="O17" s="59">
         <f t="shared" si="0"/>
         <v>173.09</v>
       </c>
-      <c r="P17" s="63">
+      <c r="P17" s="62">
         <v>167.88</v>
       </c>
-      <c r="Q17" s="48">
+      <c r="Q17" s="47">
         <v>16.670000000000002</v>
       </c>
-      <c r="R17" s="60">
+      <c r="R17" s="59">
         <f t="shared" si="1"/>
         <v>151.20999999999998</v>
       </c>
-      <c r="S17" s="64">
+      <c r="S17" s="63">
         <v>25.14</v>
       </c>
-      <c r="T17" s="65">
+      <c r="T17" s="64">
         <v>169.6</v>
       </c>
       <c r="V17" s="1">
@@ -6968,65 +6941,65 @@
       </c>
     </row>
     <row r="18" spans="1:38" ht="40.15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="77" t="s">
+      <c r="A18" s="75" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="25">
         <v>12</v>
       </c>
-      <c r="C18" s="41">
+      <c r="C18" s="40">
         <v>14</v>
       </c>
-      <c r="D18" s="42"/>
-      <c r="E18" s="41">
+      <c r="D18" s="41"/>
+      <c r="E18" s="40">
         <v>47</v>
       </c>
-      <c r="F18" s="41">
+      <c r="F18" s="40">
         <v>3</v>
       </c>
-      <c r="G18" s="41">
+      <c r="G18" s="40">
         <v>64</v>
       </c>
-      <c r="H18" s="41">
+      <c r="H18" s="40">
         <v>26903</v>
       </c>
-      <c r="I18" s="79" t="s">
+      <c r="I18" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="J18" s="63">
+      <c r="J18" s="62">
         <v>432.06</v>
       </c>
-      <c r="K18" s="48">
+      <c r="K18" s="47">
         <v>68.650000000000006</v>
       </c>
-      <c r="L18" s="60">
+      <c r="L18" s="59">
         <f t="shared" si="2"/>
         <v>363.40999999999997</v>
       </c>
-      <c r="M18" s="63">
+      <c r="M18" s="62">
         <v>164.78</v>
       </c>
-      <c r="N18" s="48">
+      <c r="N18" s="47">
         <v>16.63</v>
       </c>
-      <c r="O18" s="60">
+      <c r="O18" s="59">
         <f t="shared" si="0"/>
         <v>148.15</v>
       </c>
-      <c r="P18" s="63">
+      <c r="P18" s="62">
         <v>169.05</v>
       </c>
-      <c r="Q18" s="48">
+      <c r="Q18" s="47">
         <v>22.89</v>
       </c>
-      <c r="R18" s="60">
+      <c r="R18" s="59">
         <f t="shared" si="1"/>
         <v>146.16000000000003</v>
       </c>
-      <c r="S18" s="64">
+      <c r="S18" s="63">
         <v>30.68</v>
       </c>
-      <c r="T18" s="65">
+      <c r="T18" s="64">
         <v>136.66</v>
       </c>
       <c r="V18" s="1">
@@ -7094,63 +7067,63 @@
       </c>
     </row>
     <row r="19" spans="1:38" s="4" customFormat="1" ht="40.15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="77" t="s">
+      <c r="A19" s="75" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="25">
         <v>13</v>
       </c>
-      <c r="C19" s="41">
+      <c r="C19" s="40">
         <v>18</v>
       </c>
-      <c r="D19" s="42"/>
-      <c r="E19" s="41">
+      <c r="D19" s="41"/>
+      <c r="E19" s="40">
         <v>11</v>
       </c>
-      <c r="F19" s="41">
+      <c r="F19" s="40">
         <v>2</v>
       </c>
-      <c r="G19" s="41">
+      <c r="G19" s="40">
         <v>67</v>
       </c>
-      <c r="H19" s="41">
+      <c r="H19" s="40">
         <v>19129</v>
       </c>
-      <c r="I19" s="79"/>
-      <c r="J19" s="63">
+      <c r="I19" s="77"/>
+      <c r="J19" s="62">
         <v>529.96</v>
       </c>
-      <c r="K19" s="48">
+      <c r="K19" s="47">
         <v>56.48</v>
       </c>
-      <c r="L19" s="60">
+      <c r="L19" s="59">
         <f t="shared" si="2"/>
         <v>473.48</v>
       </c>
-      <c r="M19" s="63">
+      <c r="M19" s="62">
         <v>113.28</v>
       </c>
-      <c r="N19" s="48">
+      <c r="N19" s="47">
         <v>16.71</v>
       </c>
-      <c r="O19" s="60">
+      <c r="O19" s="59">
         <f t="shared" si="0"/>
         <v>96.57</v>
       </c>
-      <c r="P19" s="63">
+      <c r="P19" s="62">
         <v>124.36</v>
       </c>
-      <c r="Q19" s="48">
+      <c r="Q19" s="47">
         <v>15.63</v>
       </c>
-      <c r="R19" s="60">
+      <c r="R19" s="59">
         <f t="shared" si="1"/>
         <v>108.73</v>
       </c>
-      <c r="S19" s="64">
+      <c r="S19" s="63">
         <v>21.19</v>
       </c>
-      <c r="T19" s="65">
+      <c r="T19" s="64">
         <v>148.99</v>
       </c>
       <c r="U19" s="2"/>
@@ -7220,63 +7193,63 @@
       <c r="AL19" s="1"/>
     </row>
     <row r="20" spans="1:38" ht="40.15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="78" t="s">
+      <c r="A20" s="76" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="25">
         <v>16</v>
       </c>
-      <c r="C20" s="41">
+      <c r="C20" s="40">
         <v>16</v>
       </c>
-      <c r="D20" s="42"/>
-      <c r="E20" s="41">
+      <c r="D20" s="41"/>
+      <c r="E20" s="40">
         <v>20</v>
       </c>
-      <c r="F20" s="41">
+      <c r="F20" s="40">
         <v>3</v>
       </c>
-      <c r="G20" s="41">
+      <c r="G20" s="40">
         <v>58</v>
       </c>
-      <c r="H20" s="41">
+      <c r="H20" s="40">
         <v>15880</v>
       </c>
-      <c r="I20" s="79"/>
-      <c r="J20" s="66">
+      <c r="I20" s="77"/>
+      <c r="J20" s="65">
         <v>439.53</v>
       </c>
-      <c r="K20" s="67">
+      <c r="K20" s="66">
         <v>68.959999999999994</v>
       </c>
-      <c r="L20" s="60">
+      <c r="L20" s="59">
         <f t="shared" si="2"/>
         <v>370.57</v>
       </c>
-      <c r="M20" s="66">
+      <c r="M20" s="65">
         <v>134.43</v>
       </c>
-      <c r="N20" s="67">
+      <c r="N20" s="66">
         <v>15.6</v>
       </c>
-      <c r="O20" s="60">
+      <c r="O20" s="59">
         <f t="shared" si="0"/>
         <v>118.83000000000001</v>
       </c>
-      <c r="P20" s="66">
+      <c r="P20" s="65">
         <v>120.34</v>
       </c>
-      <c r="Q20" s="67">
+      <c r="Q20" s="66">
         <v>15.61</v>
       </c>
-      <c r="R20" s="60">
+      <c r="R20" s="59">
         <f t="shared" si="1"/>
         <v>104.73</v>
       </c>
-      <c r="S20" s="64">
+      <c r="S20" s="63">
         <v>20.55</v>
       </c>
-      <c r="T20" s="65">
+      <c r="T20" s="64">
         <v>127.87</v>
       </c>
       <c r="V20" s="1">
@@ -7366,7 +7339,7 @@
     <row r="24" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="T26" s="87">
+      <c r="T26" s="85">
         <f>AVERAGE(T13:T20)</f>
         <v>142.63499999999999</v>
       </c>
@@ -7475,268 +7448,253 @@
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="B5" s="30"/>
+      <c r="B5" s="29"/>
       <c r="D5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>40779</v>
       </c>
-      <c r="F5" s="24"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
+      <c r="F5" s="23"/>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="B6" s="30"/>
+      <c r="B6" s="29"/>
       <c r="D6" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
     </row>
     <row r="8" spans="1:39" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="30"/>
+      <c r="B8" s="29"/>
       <c r="D8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="24"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
+      <c r="F8" s="23"/>
       <c r="M8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="N8" s="9">
+      <c r="N8" s="8">
         <v>40788</v>
       </c>
-      <c r="O8" s="24"/>
+      <c r="O8" s="23"/>
     </row>
     <row r="9" spans="1:39" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="30"/>
+      <c r="B9" s="29"/>
       <c r="D9" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
     </row>
     <row r="10" spans="1:39" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="5"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15"/>
+      <c r="R10" s="15"/>
+      <c r="S10" s="15"/>
     </row>
     <row r="11" spans="1:39" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D11" s="8"/>
-      <c r="E11" s="10" t="s">
+      <c r="D11" s="7"/>
+      <c r="E11" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="18"/>
-      <c r="O11" s="86" t="s">
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="84" t="s">
         <v>61</v>
       </c>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19"/>
-      <c r="S11" s="19"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="18"/>
     </row>
     <row r="12" spans="1:39" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="13" t="s">
+      <c r="D12" s="13"/>
+      <c r="E12" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="H12" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I12" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="J12" s="13" t="s">
+      <c r="J12" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="K12" s="14"/>
-      <c r="L12" s="32" t="s">
+      <c r="K12" s="13"/>
+      <c r="L12" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="M12" s="33" t="s">
+      <c r="M12" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="N12" s="81" t="s">
+      <c r="N12" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="O12" s="32" t="s">
+      <c r="O12" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="P12" s="33" t="s">
+      <c r="P12" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="Q12" s="34" t="s">
+      <c r="Q12" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="R12" s="32" t="s">
+      <c r="R12" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="S12" s="33" t="s">
+      <c r="S12" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="T12" s="34" t="s">
+      <c r="T12" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="U12" s="35" t="s">
+      <c r="U12" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="V12" s="36" t="s">
+      <c r="V12" s="35" t="s">
         <v>39</v>
       </c>
       <c r="AA12" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="AB12" s="97" t="s">
+      <c r="AB12" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="AC12" s="97" t="s">
+      <c r="AC12" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="AD12" s="97" t="s">
+      <c r="AD12" s="86" t="s">
         <v>74</v>
       </c>
-      <c r="AE12" s="97" t="s">
+      <c r="AE12" s="86" t="s">
         <v>75</v>
       </c>
-      <c r="AF12" s="97" t="s">
+      <c r="AF12" s="86" t="s">
         <v>66</v>
       </c>
-      <c r="AG12" s="97" t="s">
+      <c r="AG12" s="86" t="s">
         <v>67</v>
       </c>
-      <c r="AH12" s="97" t="s">
+      <c r="AH12" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="AI12" s="97" t="s">
+      <c r="AI12" s="86" t="s">
         <v>69</v>
       </c>
-      <c r="AJ12" s="97" t="s">
+      <c r="AJ12" s="86" t="s">
         <v>70</v>
       </c>
-      <c r="AK12" s="97" t="s">
+      <c r="AK12" s="86" t="s">
         <v>71</v>
       </c>
-      <c r="AL12" s="97" t="s">
+      <c r="AL12" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="AM12" s="97" t="s">
+      <c r="AM12" s="86" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:39" ht="40.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="80">
+      <c r="A13" s="78">
         <v>40779</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="25">
         <v>2</v>
       </c>
-      <c r="C13" s="41">
+      <c r="C13" s="40">
         <v>14</v>
       </c>
-      <c r="D13" s="42"/>
-      <c r="E13" s="41">
+      <c r="D13" s="41"/>
+      <c r="E13" s="40">
         <v>36</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="40">
         <v>1</v>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="40">
         <v>89</v>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="40">
         <v>26</v>
       </c>
-      <c r="I13" s="41">
+      <c r="I13" s="40">
         <v>32744</v>
       </c>
-      <c r="J13" s="94" t="s">
+      <c r="J13" s="98" t="s">
         <v>59</v>
       </c>
-      <c r="K13" s="21">
+      <c r="K13" s="20">
         <v>2</v>
       </c>
-      <c r="L13" s="58">
+      <c r="L13" s="57">
         <v>712.14</v>
       </c>
-      <c r="M13" s="59">
+      <c r="M13" s="58">
         <v>69.31</v>
       </c>
-      <c r="N13" s="82">
+      <c r="N13" s="80">
         <f>L13-M13</f>
         <v>642.82999999999993</v>
       </c>
-      <c r="O13" s="58">
+      <c r="O13" s="57">
         <v>245.45</v>
       </c>
-      <c r="P13" s="59">
+      <c r="P13" s="58">
         <v>23.11</v>
       </c>
-      <c r="Q13" s="82">
+      <c r="Q13" s="80">
         <f>O13-P13</f>
         <v>222.33999999999997</v>
       </c>
-      <c r="R13" s="58">
+      <c r="R13" s="57">
         <v>215.33</v>
       </c>
-      <c r="S13" s="59">
+      <c r="S13" s="58">
         <v>32.270000000000003</v>
       </c>
-      <c r="T13" s="83">
+      <c r="T13" s="81">
         <f t="shared" ref="T13:T20" si="0">R13-S13</f>
         <v>183.06</v>
       </c>
-      <c r="U13" s="61">
+      <c r="U13" s="60">
         <v>35.67</v>
       </c>
-      <c r="V13" s="62">
+      <c r="V13" s="61">
         <v>360.34</v>
       </c>
       <c r="X13" s="1">
@@ -7805,69 +7763,69 @@
       </c>
     </row>
     <row r="14" spans="1:39" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="80">
+      <c r="A14" s="78">
         <v>40780</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="25">
         <v>4</v>
       </c>
-      <c r="C14" s="41">
+      <c r="C14" s="40">
         <v>13</v>
       </c>
-      <c r="D14" s="42"/>
-      <c r="E14" s="41">
+      <c r="D14" s="41"/>
+      <c r="E14" s="40">
         <v>104</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="40">
         <v>3</v>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="40">
         <v>95</v>
       </c>
-      <c r="H14" s="41">
+      <c r="H14" s="40">
         <v>34</v>
       </c>
-      <c r="I14" s="41">
+      <c r="I14" s="40">
         <v>35266</v>
       </c>
-      <c r="J14" s="95"/>
-      <c r="K14" s="21">
+      <c r="J14" s="99"/>
+      <c r="K14" s="20">
         <v>4</v>
       </c>
-      <c r="L14" s="63">
+      <c r="L14" s="62">
         <v>615.05999999999995</v>
       </c>
-      <c r="M14" s="48">
+      <c r="M14" s="47">
         <v>69.75</v>
       </c>
-      <c r="N14" s="83">
+      <c r="N14" s="81">
         <f t="shared" ref="N14:N20" si="1">L14-M14</f>
         <v>545.30999999999995</v>
       </c>
-      <c r="O14" s="63">
+      <c r="O14" s="62">
         <v>236.51</v>
       </c>
-      <c r="P14" s="48">
+      <c r="P14" s="47">
         <v>17.03</v>
       </c>
-      <c r="Q14" s="83">
+      <c r="Q14" s="81">
         <f>O14-P14</f>
         <v>219.48</v>
       </c>
-      <c r="R14" s="63">
+      <c r="R14" s="62">
         <v>217.46</v>
       </c>
-      <c r="S14" s="48">
+      <c r="S14" s="47">
         <v>17.190000000000001</v>
       </c>
-      <c r="T14" s="83">
+      <c r="T14" s="81">
         <f t="shared" si="0"/>
         <v>200.27</v>
       </c>
-      <c r="U14" s="64">
+      <c r="U14" s="63">
         <v>41.53</v>
       </c>
-      <c r="V14" s="65">
+      <c r="V14" s="64">
         <v>428.87</v>
       </c>
       <c r="X14" s="1">
@@ -7936,69 +7894,69 @@
       </c>
     </row>
     <row r="15" spans="1:39" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="80">
+      <c r="A15" s="78">
         <v>40780</v>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="25">
         <v>6</v>
       </c>
-      <c r="C15" s="41">
+      <c r="C15" s="40">
         <v>15</v>
       </c>
-      <c r="D15" s="42"/>
-      <c r="E15" s="41">
+      <c r="D15" s="41"/>
+      <c r="E15" s="40">
         <v>112</v>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="40">
         <v>7</v>
       </c>
-      <c r="G15" s="41">
+      <c r="G15" s="40">
         <v>60</v>
       </c>
-      <c r="H15" s="41">
+      <c r="H15" s="40">
         <v>33</v>
       </c>
-      <c r="I15" s="41">
+      <c r="I15" s="40">
         <v>31067</v>
       </c>
-      <c r="J15" s="95"/>
-      <c r="K15" s="21">
+      <c r="J15" s="99"/>
+      <c r="K15" s="20">
         <v>6</v>
       </c>
-      <c r="L15" s="63">
+      <c r="L15" s="62">
         <v>801.48</v>
       </c>
-      <c r="M15" s="48">
+      <c r="M15" s="47">
         <v>69.34</v>
       </c>
-      <c r="N15" s="83">
+      <c r="N15" s="81">
         <f t="shared" si="1"/>
         <v>732.14</v>
       </c>
-      <c r="O15" s="63">
+      <c r="O15" s="62">
         <v>192.99</v>
       </c>
-      <c r="P15" s="48">
+      <c r="P15" s="47">
         <v>17.11</v>
       </c>
-      <c r="Q15" s="83">
+      <c r="Q15" s="81">
         <f>O15-P15</f>
         <v>175.88</v>
       </c>
-      <c r="R15" s="63">
+      <c r="R15" s="62">
         <v>191.9</v>
       </c>
-      <c r="S15" s="48">
+      <c r="S15" s="47">
         <v>17.09</v>
       </c>
-      <c r="T15" s="83">
+      <c r="T15" s="81">
         <f t="shared" si="0"/>
         <v>174.81</v>
       </c>
-      <c r="U15" s="64">
+      <c r="U15" s="63">
         <v>35.24</v>
       </c>
-      <c r="V15" s="65">
+      <c r="V15" s="64">
         <v>328.24</v>
       </c>
       <c r="X15" s="1">
@@ -8067,68 +8025,68 @@
       </c>
     </row>
     <row r="16" spans="1:39" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="80">
+      <c r="A16" s="78">
         <v>40780</v>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="25">
         <v>8</v>
       </c>
-      <c r="C16" s="41">
+      <c r="C16" s="40">
         <v>20</v>
       </c>
-      <c r="D16" s="42"/>
-      <c r="E16" s="41">
+      <c r="D16" s="41"/>
+      <c r="E16" s="40">
         <v>49</v>
       </c>
-      <c r="F16" s="41">
+      <c r="F16" s="40">
         <v>0</v>
       </c>
-      <c r="G16" s="41">
+      <c r="G16" s="40">
         <v>37</v>
       </c>
-      <c r="H16" s="41">
+      <c r="H16" s="40">
         <v>3.2</v>
       </c>
-      <c r="I16" s="41">
+      <c r="I16" s="40">
         <v>20081</v>
       </c>
-      <c r="J16" s="95"/>
-      <c r="K16" s="21">
+      <c r="J16" s="99"/>
+      <c r="K16" s="20">
         <v>8</v>
       </c>
-      <c r="L16" s="63">
+      <c r="L16" s="62">
         <v>1039.99</v>
       </c>
-      <c r="M16" s="48">
+      <c r="M16" s="47">
         <v>70.28</v>
       </c>
-      <c r="N16" s="83">
+      <c r="N16" s="81">
         <f t="shared" si="1"/>
         <v>969.71</v>
       </c>
-      <c r="O16" s="85" t="s">
+      <c r="O16" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="P16" s="85" t="s">
+      <c r="P16" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="Q16" s="83">
+      <c r="Q16" s="81">
         <v>130.49</v>
       </c>
-      <c r="R16" s="63">
+      <c r="R16" s="62">
         <v>135.43</v>
       </c>
-      <c r="S16" s="48">
+      <c r="S16" s="47">
         <v>17.12</v>
       </c>
-      <c r="T16" s="83">
+      <c r="T16" s="81">
         <f t="shared" si="0"/>
         <v>118.31</v>
       </c>
-      <c r="U16" s="64">
+      <c r="U16" s="63">
         <v>22.89</v>
       </c>
-      <c r="V16" s="65">
+      <c r="V16" s="64">
         <v>265.76</v>
       </c>
       <c r="X16" s="1">
@@ -8197,69 +8155,69 @@
       </c>
     </row>
     <row r="17" spans="1:39" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="80">
+      <c r="A17" s="78">
         <v>40781</v>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="25">
         <v>9</v>
       </c>
-      <c r="C17" s="41">
+      <c r="C17" s="40">
         <v>17</v>
       </c>
-      <c r="D17" s="42"/>
-      <c r="E17" s="41">
+      <c r="D17" s="41"/>
+      <c r="E17" s="40">
         <v>127</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="40">
         <v>3</v>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="40">
         <v>54</v>
       </c>
-      <c r="H17" s="41">
+      <c r="H17" s="40">
         <v>29</v>
       </c>
-      <c r="I17" s="41">
+      <c r="I17" s="40">
         <v>38356</v>
       </c>
-      <c r="J17" s="95"/>
-      <c r="K17" s="21">
+      <c r="J17" s="99"/>
+      <c r="K17" s="20">
         <v>9</v>
       </c>
-      <c r="L17" s="63">
+      <c r="L17" s="62">
         <v>789.2</v>
       </c>
-      <c r="M17" s="48">
+      <c r="M17" s="47">
         <v>69.819999999999993</v>
       </c>
-      <c r="N17" s="83">
+      <c r="N17" s="81">
         <f t="shared" si="1"/>
         <v>719.38000000000011</v>
       </c>
-      <c r="O17" s="63">
+      <c r="O17" s="62">
         <v>189.98</v>
       </c>
-      <c r="P17" s="48">
+      <c r="P17" s="47">
         <v>16.91</v>
       </c>
-      <c r="Q17" s="83">
+      <c r="Q17" s="81">
         <f>O17-P17</f>
         <v>173.07</v>
       </c>
-      <c r="R17" s="63">
+      <c r="R17" s="62">
         <v>186</v>
       </c>
-      <c r="S17" s="48">
+      <c r="S17" s="47">
         <v>17.07</v>
       </c>
-      <c r="T17" s="83">
+      <c r="T17" s="81">
         <f t="shared" si="0"/>
         <v>168.93</v>
       </c>
-      <c r="U17" s="64">
+      <c r="U17" s="63">
         <v>35.200000000000003</v>
       </c>
-      <c r="V17" s="65">
+      <c r="V17" s="64">
         <v>256.45</v>
       </c>
       <c r="X17" s="1">
@@ -8328,68 +8286,68 @@
       </c>
     </row>
     <row r="18" spans="1:39" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="80">
+      <c r="A18" s="78">
         <v>40781</v>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="25">
         <v>11</v>
       </c>
-      <c r="C18" s="41">
+      <c r="C18" s="40">
         <v>17</v>
       </c>
-      <c r="D18" s="42"/>
-      <c r="E18" s="41">
+      <c r="D18" s="41"/>
+      <c r="E18" s="40">
         <v>66</v>
       </c>
-      <c r="F18" s="41">
+      <c r="F18" s="40">
         <v>6</v>
       </c>
-      <c r="G18" s="41">
+      <c r="G18" s="40">
         <v>60</v>
       </c>
-      <c r="H18" s="41">
+      <c r="H18" s="40">
         <v>15</v>
       </c>
-      <c r="I18" s="41">
+      <c r="I18" s="40">
         <v>26554</v>
       </c>
-      <c r="J18" s="95"/>
-      <c r="K18" s="21">
+      <c r="J18" s="99"/>
+      <c r="K18" s="20">
         <v>11</v>
       </c>
-      <c r="L18" s="63">
+      <c r="L18" s="62">
         <v>882.74</v>
       </c>
-      <c r="M18" s="48">
+      <c r="M18" s="47">
         <v>69.599999999999994</v>
       </c>
-      <c r="N18" s="83">
+      <c r="N18" s="81">
         <f t="shared" si="1"/>
         <v>813.14</v>
       </c>
-      <c r="O18" s="85" t="s">
+      <c r="O18" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="P18" s="85" t="s">
+      <c r="P18" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="Q18" s="83">
+      <c r="Q18" s="81">
         <v>162.59</v>
       </c>
-      <c r="R18" s="63">
+      <c r="R18" s="62">
         <v>164.74</v>
       </c>
-      <c r="S18" s="48">
+      <c r="S18" s="47">
         <v>15.99</v>
       </c>
-      <c r="T18" s="83">
+      <c r="T18" s="81">
         <f t="shared" si="0"/>
         <v>148.75</v>
       </c>
-      <c r="U18" s="64">
+      <c r="U18" s="63">
         <v>30.75</v>
       </c>
-      <c r="V18" s="65">
+      <c r="V18" s="64">
         <v>319.17</v>
       </c>
       <c r="X18" s="1">
@@ -8458,69 +8416,69 @@
       </c>
     </row>
     <row r="19" spans="1:39" s="4" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="80">
+      <c r="A19" s="78">
         <v>40781</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="25">
         <v>14</v>
       </c>
-      <c r="C19" s="41">
+      <c r="C19" s="40">
         <v>17</v>
       </c>
-      <c r="D19" s="42"/>
-      <c r="E19" s="41">
+      <c r="D19" s="41"/>
+      <c r="E19" s="40">
         <v>97</v>
       </c>
-      <c r="F19" s="41">
+      <c r="F19" s="40">
         <v>2</v>
       </c>
-      <c r="G19" s="41">
+      <c r="G19" s="40">
         <v>63</v>
       </c>
-      <c r="H19" s="41">
+      <c r="H19" s="40">
         <v>15</v>
       </c>
-      <c r="I19" s="41">
+      <c r="I19" s="40">
         <v>23640</v>
       </c>
-      <c r="J19" s="95"/>
-      <c r="K19" s="21">
+      <c r="J19" s="99"/>
+      <c r="K19" s="20">
         <v>14</v>
       </c>
-      <c r="L19" s="63">
+      <c r="L19" s="62">
         <v>734.42</v>
       </c>
-      <c r="M19" s="48">
+      <c r="M19" s="47">
         <v>69.69</v>
       </c>
-      <c r="N19" s="83">
+      <c r="N19" s="81">
         <f t="shared" si="1"/>
         <v>664.73</v>
       </c>
-      <c r="O19" s="63">
+      <c r="O19" s="62">
         <v>174.38</v>
       </c>
-      <c r="P19" s="63">
+      <c r="P19" s="62">
         <v>16.649999999999999</v>
       </c>
-      <c r="Q19" s="83">
+      <c r="Q19" s="81">
         <f>O19-P19</f>
         <v>157.72999999999999</v>
       </c>
-      <c r="R19" s="63">
+      <c r="R19" s="62">
         <v>141.47999999999999</v>
       </c>
-      <c r="S19" s="48">
+      <c r="S19" s="47">
         <v>16.63</v>
       </c>
-      <c r="T19" s="83">
+      <c r="T19" s="81">
         <f t="shared" si="0"/>
         <v>124.85</v>
       </c>
-      <c r="U19" s="64">
+      <c r="U19" s="63">
         <v>31.06</v>
       </c>
-      <c r="V19" s="65">
+      <c r="V19" s="64">
         <v>183.11</v>
       </c>
       <c r="W19" s="2"/>
@@ -8590,68 +8548,68 @@
       </c>
     </row>
     <row r="20" spans="1:39" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="80">
+      <c r="A20" s="78">
         <v>40781</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="25">
         <v>15</v>
       </c>
-      <c r="C20" s="41">
+      <c r="C20" s="40">
         <v>20</v>
       </c>
-      <c r="D20" s="42"/>
-      <c r="E20" s="41">
+      <c r="D20" s="41"/>
+      <c r="E20" s="40">
         <v>114</v>
       </c>
-      <c r="F20" s="41">
+      <c r="F20" s="40">
         <v>2</v>
       </c>
-      <c r="G20" s="41">
+      <c r="G20" s="40">
         <v>86</v>
       </c>
-      <c r="H20" s="41">
+      <c r="H20" s="40">
         <v>14</v>
       </c>
-      <c r="I20" s="41">
+      <c r="I20" s="40">
         <v>29178</v>
       </c>
-      <c r="J20" s="96"/>
-      <c r="K20" s="21">
+      <c r="J20" s="100"/>
+      <c r="K20" s="20">
         <v>15</v>
       </c>
-      <c r="L20" s="66">
+      <c r="L20" s="65">
         <v>743.08</v>
       </c>
-      <c r="M20" s="67">
+      <c r="M20" s="66">
         <v>69.680000000000007</v>
       </c>
-      <c r="N20" s="84">
+      <c r="N20" s="82">
         <f t="shared" si="1"/>
         <v>673.40000000000009</v>
       </c>
-      <c r="O20" s="85" t="s">
+      <c r="O20" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="P20" s="85" t="s">
+      <c r="P20" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="Q20" s="84">
+      <c r="Q20" s="82">
         <v>209.96</v>
       </c>
-      <c r="R20" s="66">
+      <c r="R20" s="65">
         <v>195.75</v>
       </c>
-      <c r="S20" s="67">
+      <c r="S20" s="66">
         <v>15.99</v>
       </c>
-      <c r="T20" s="83">
+      <c r="T20" s="81">
         <f t="shared" si="0"/>
         <v>179.76</v>
       </c>
-      <c r="U20" s="64">
+      <c r="U20" s="63">
         <v>38.159999999999997</v>
       </c>
-      <c r="V20" s="65">
+      <c r="V20" s="64">
         <v>263.04000000000002</v>
       </c>
       <c r="X20" s="1">
@@ -8739,7 +8697,7 @@
     </row>
     <row r="22" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="N23" s="87">
+      <c r="N23" s="85">
         <f>AVERAGE(N13:N20)/(100*102)</f>
         <v>7.0596078431372541E-2</v>
       </c>
@@ -8801,7 +8759,7 @@
         <f t="shared" si="19"/>
         <v>7.9601990049751242E-2</v>
       </c>
-      <c r="V27" s="87">
+      <c r="V27" s="85">
         <f>AVERAGE(V13:V20)</f>
         <v>300.6225</v>
       </c>
@@ -8877,7 +8835,7 @@
       <c r="T54" s="1">
         <v>152</v>
       </c>
-      <c r="U54" s="87">
+      <c r="U54" s="85">
         <f>'1June11'!N25</f>
         <v>5.9999999999999991E-2</v>
       </c>
@@ -8886,7 +8844,7 @@
       <c r="T55" s="1">
         <v>181</v>
       </c>
-      <c r="U55" s="87">
+      <c r="U55" s="85">
         <f>'30June11'!Q26</f>
         <v>18.127499999999998</v>
       </c>
@@ -8895,7 +8853,7 @@
       <c r="T56" s="1">
         <v>208</v>
       </c>
-      <c r="U56" s="87">
+      <c r="U56" s="85">
         <f>'27July11'!T26</f>
         <v>142.63499999999999</v>
       </c>
@@ -8904,7 +8862,7 @@
       <c r="T57" s="1">
         <v>236</v>
       </c>
-      <c r="U57" s="87">
+      <c r="U57" s="85">
         <f>V27</f>
         <v>300.6225</v>
       </c>
@@ -8988,326 +8946,311 @@
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B5" s="30"/>
-      <c r="C5" s="30" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="29" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="6"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="23"/>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B6" s="30"/>
-      <c r="C6" s="30" t="s">
+      <c r="B6" s="29"/>
+      <c r="C6" s="29" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
     </row>
     <row r="8" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="30"/>
-      <c r="C8" s="30" t="s">
+      <c r="B8" s="29"/>
+      <c r="C8" s="29" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="6"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="23"/>
       <c r="M8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="N8" s="9"/>
-      <c r="O8" s="24"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="23"/>
     </row>
     <row r="9" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="30"/>
-      <c r="C9" s="30" t="s">
+      <c r="B9" s="29"/>
+      <c r="C9" s="29" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
       <c r="N9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="5"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="16"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15"/>
+      <c r="R10" s="15"/>
+      <c r="S10" s="15"/>
+      <c r="T10" s="15"/>
     </row>
     <row r="11" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D11" s="8"/>
-      <c r="E11" s="10" t="s">
+      <c r="D11" s="7"/>
+      <c r="E11" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="18"/>
-      <c r="O11" s="18"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19"/>
-      <c r="S11" s="19"/>
-      <c r="T11" s="19"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="18"/>
+      <c r="T11" s="18"/>
     </row>
     <row r="12" spans="2:21" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="13" t="s">
+      <c r="D12" s="13"/>
+      <c r="E12" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="H12" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I12" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="J12" s="13"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="27" t="s">
+      <c r="J12" s="12"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="M12" s="31" t="s">
+      <c r="M12" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="N12" s="27" t="s">
+      <c r="N12" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="31" t="s">
+      <c r="O12" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="P12" s="27" t="s">
+      <c r="P12" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="Q12" s="31" t="s">
+      <c r="Q12" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="R12" s="28" t="s">
+      <c r="R12" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="S12" s="15" t="s">
+      <c r="S12" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="T12" s="29" t="s">
+      <c r="T12" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="U12" s="15" t="s">
+      <c r="U12" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="2:21" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="21">
+      <c r="B13" s="20">
         <v>2</v>
       </c>
-      <c r="C13" s="41"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="42"/>
-      <c r="L13" s="48"/>
-      <c r="M13" s="48"/>
-      <c r="N13" s="48"/>
-      <c r="O13" s="48"/>
-      <c r="P13" s="48"/>
-      <c r="Q13" s="48"/>
-      <c r="R13" s="48"/>
-      <c r="S13" s="48"/>
-      <c r="T13" s="48"/>
-      <c r="U13" s="68"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="47"/>
+      <c r="M13" s="47"/>
+      <c r="N13" s="47"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="47"/>
+      <c r="Q13" s="47"/>
+      <c r="R13" s="47"/>
+      <c r="S13" s="47"/>
+      <c r="T13" s="47"/>
+      <c r="U13" s="67"/>
     </row>
     <row r="14" spans="2:21" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="21">
+      <c r="B14" s="20">
         <v>4</v>
       </c>
-      <c r="C14" s="41"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="41"/>
-      <c r="K14" s="42"/>
-      <c r="L14" s="48"/>
-      <c r="M14" s="48"/>
-      <c r="N14" s="48"/>
-      <c r="O14" s="48"/>
-      <c r="P14" s="48"/>
-      <c r="Q14" s="48"/>
-      <c r="R14" s="48"/>
-      <c r="S14" s="48"/>
-      <c r="T14" s="48"/>
-      <c r="U14" s="68"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="41"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="47"/>
+      <c r="N14" s="47"/>
+      <c r="O14" s="47"/>
+      <c r="P14" s="47"/>
+      <c r="Q14" s="47"/>
+      <c r="R14" s="47"/>
+      <c r="S14" s="47"/>
+      <c r="T14" s="47"/>
+      <c r="U14" s="67"/>
     </row>
     <row r="15" spans="2:21" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="21">
+      <c r="B15" s="20">
         <v>6</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="41"/>
-      <c r="K15" s="42"/>
-      <c r="L15" s="48"/>
-      <c r="M15" s="48"/>
-      <c r="N15" s="48"/>
-      <c r="O15" s="48"/>
-      <c r="P15" s="48"/>
-      <c r="Q15" s="48"/>
-      <c r="R15" s="48"/>
-      <c r="S15" s="48"/>
-      <c r="T15" s="48"/>
-      <c r="U15" s="68"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="47"/>
+      <c r="M15" s="47"/>
+      <c r="N15" s="47"/>
+      <c r="O15" s="47"/>
+      <c r="P15" s="47"/>
+      <c r="Q15" s="47"/>
+      <c r="R15" s="47"/>
+      <c r="S15" s="47"/>
+      <c r="T15" s="47"/>
+      <c r="U15" s="67"/>
     </row>
     <row r="16" spans="2:21" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="21">
+      <c r="B16" s="20">
         <v>8</v>
       </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="42"/>
-      <c r="L16" s="48"/>
-      <c r="M16" s="48"/>
-      <c r="N16" s="48"/>
-      <c r="O16" s="48"/>
-      <c r="P16" s="48"/>
-      <c r="Q16" s="48"/>
-      <c r="R16" s="48"/>
-      <c r="S16" s="48"/>
-      <c r="T16" s="48"/>
-      <c r="U16" s="68"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="47"/>
+      <c r="M16" s="47"/>
+      <c r="N16" s="47"/>
+      <c r="O16" s="47"/>
+      <c r="P16" s="47"/>
+      <c r="Q16" s="47"/>
+      <c r="R16" s="47"/>
+      <c r="S16" s="47"/>
+      <c r="T16" s="47"/>
+      <c r="U16" s="67"/>
     </row>
     <row r="17" spans="2:29" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="21">
+      <c r="B17" s="20">
         <v>9</v>
       </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="41"/>
-      <c r="J17" s="41"/>
-      <c r="K17" s="42"/>
-      <c r="L17" s="48"/>
-      <c r="M17" s="48"/>
-      <c r="N17" s="48"/>
-      <c r="O17" s="48"/>
-      <c r="P17" s="48"/>
-      <c r="Q17" s="48"/>
-      <c r="R17" s="48"/>
-      <c r="S17" s="48"/>
-      <c r="T17" s="48"/>
-      <c r="U17" s="68"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="40"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="47"/>
+      <c r="M17" s="47"/>
+      <c r="N17" s="47"/>
+      <c r="O17" s="47"/>
+      <c r="P17" s="47"/>
+      <c r="Q17" s="47"/>
+      <c r="R17" s="47"/>
+      <c r="S17" s="47"/>
+      <c r="T17" s="47"/>
+      <c r="U17" s="67"/>
     </row>
     <row r="18" spans="2:29" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="21">
+      <c r="B18" s="20">
         <v>11</v>
       </c>
-      <c r="C18" s="41"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="48"/>
-      <c r="M18" s="48"/>
-      <c r="N18" s="48"/>
-      <c r="O18" s="48"/>
-      <c r="P18" s="48"/>
-      <c r="Q18" s="48"/>
-      <c r="R18" s="48"/>
-      <c r="S18" s="48"/>
-      <c r="T18" s="48"/>
-      <c r="U18" s="68"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="47"/>
+      <c r="M18" s="47"/>
+      <c r="N18" s="47"/>
+      <c r="O18" s="47"/>
+      <c r="P18" s="47"/>
+      <c r="Q18" s="47"/>
+      <c r="R18" s="47"/>
+      <c r="S18" s="47"/>
+      <c r="T18" s="47"/>
+      <c r="U18" s="67"/>
     </row>
     <row r="19" spans="2:29" s="4" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="21">
+      <c r="B19" s="20">
         <v>14</v>
       </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="41"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="48"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="48"/>
-      <c r="R19" s="48"/>
-      <c r="S19" s="48"/>
-      <c r="T19" s="48"/>
-      <c r="U19" s="68"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="40"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="47"/>
+      <c r="M19" s="47"/>
+      <c r="N19" s="47"/>
+      <c r="O19" s="47"/>
+      <c r="P19" s="47"/>
+      <c r="Q19" s="47"/>
+      <c r="R19" s="47"/>
+      <c r="S19" s="47"/>
+      <c r="T19" s="47"/>
+      <c r="U19" s="67"/>
       <c r="V19" s="2"/>
       <c r="W19" s="2"/>
       <c r="X19" s="2"/>
@@ -9318,28 +9261,28 @@
       <c r="AC19" s="3"/>
     </row>
     <row r="20" spans="2:29" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="21">
+      <c r="B20" s="20">
         <v>15</v>
       </c>
-      <c r="C20" s="41"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="41"/>
-      <c r="J20" s="41"/>
-      <c r="K20" s="42"/>
-      <c r="L20" s="48"/>
-      <c r="M20" s="48"/>
-      <c r="N20" s="48"/>
-      <c r="O20" s="48"/>
-      <c r="P20" s="48"/>
-      <c r="Q20" s="48"/>
-      <c r="R20" s="48"/>
-      <c r="S20" s="48"/>
-      <c r="T20" s="48"/>
-      <c r="U20" s="68"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="41"/>
+      <c r="L20" s="47"/>
+      <c r="M20" s="47"/>
+      <c r="N20" s="47"/>
+      <c r="O20" s="47"/>
+      <c r="P20" s="47"/>
+      <c r="Q20" s="47"/>
+      <c r="R20" s="47"/>
+      <c r="S20" s="47"/>
+      <c r="T20" s="47"/>
+      <c r="U20" s="67"/>
     </row>
     <row r="21" spans="2:29" ht="29.85" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="22" spans="2:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
